--- a/data/seguimiento_pad.xlsx
+++ b/data/seguimiento_pad.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juanm\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDF84F7D-9EEF-4C24-9FCF-6A4622696099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACF55AC9-A3D1-41E0-B640-55BC141D3C82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Bitácora diaria'!$A$1:$J$127</definedName>
   </definedNames>
-  <calcPr calcId="191028" iterateDelta="1E-4"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1146" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="272">
   <si>
     <t>UNIVERSIDAD DE CUNDINAMARCA · CADI · MEDIT</t>
   </si>
@@ -898,7 +898,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="dd/mm"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1638,7 +1638,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="162">
+  <cellXfs count="161">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1980,9 +1980,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
@@ -5391,7 +5388,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:H35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5546875" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -5399,27 +5396,27 @@
     <col min="8" max="8" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:4" ht="21">
+    <row r="3" spans="2:4" ht="21" x14ac:dyDescent="0.4">
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:4">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:4">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="2:4">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>4</v>
       </c>
@@ -5430,7 +5427,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="2:4">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B8" s="5" t="s">
         <v>7</v>
       </c>
@@ -5442,7 +5439,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="2:4">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
@@ -5454,7 +5451,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="2:4">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B10" s="5" t="s">
         <v>10</v>
       </c>
@@ -5466,7 +5463,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:4">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B11" s="5" t="s">
         <v>12</v>
       </c>
@@ -5478,7 +5475,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:4">
+    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B12" s="5" t="s">
         <v>13</v>
       </c>
@@ -5490,7 +5487,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:4">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B13" s="5" t="s">
         <v>14</v>
       </c>
@@ -5502,7 +5499,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="2:4">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B14" s="5" t="s">
         <v>16</v>
       </c>
@@ -5514,7 +5511,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="2:4">
+    <row r="15" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B15" s="5" t="s">
         <v>17</v>
       </c>
@@ -5526,7 +5523,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="2:4">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B16" s="5" t="s">
         <v>18</v>
       </c>
@@ -5538,12 +5535,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="2:8">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
         <v>21</v>
       </c>
@@ -5566,7 +5563,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="2:8">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="10" t="s">
         <v>28</v>
       </c>
@@ -5593,7 +5590,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="10" t="s">
         <v>30</v>
       </c>
@@ -5620,7 +5617,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="10" t="s">
         <v>32</v>
       </c>
@@ -5647,7 +5644,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="10" t="s">
         <v>34</v>
       </c>
@@ -5674,7 +5671,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="2:8">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="13" t="s">
         <v>36</v>
       </c>
@@ -5697,12 +5694,12 @@
       </c>
       <c r="H24" s="14"/>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
         <v>38</v>
       </c>
@@ -5716,7 +5713,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="16" t="s">
         <v>40</v>
       </c>
@@ -5733,7 +5730,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B30" s="17" t="s">
         <v>41</v>
       </c>
@@ -5750,7 +5747,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B31" s="18" t="s">
         <v>42</v>
       </c>
@@ -5767,7 +5764,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="32" spans="2:8">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B32" s="19" t="s">
         <v>43</v>
       </c>
@@ -5784,7 +5781,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="35" spans="2:2">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B35" s="20" t="s">
         <v>44</v>
       </c>
@@ -5798,7 +5795,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:E26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5546875" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -5807,12 +5804,12 @@
     <col min="5" max="5" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="16.8">
+    <row r="2" spans="2:4" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B2" s="21" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="2:4">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>46</v>
       </c>
@@ -5823,7 +5820,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="2:4">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B4" s="5" t="s">
         <v>48</v>
       </c>
@@ -5834,7 +5831,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="2:4">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B5" s="5" t="s">
         <v>50</v>
       </c>
@@ -5845,7 +5842,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="2:4">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>52</v>
       </c>
@@ -5856,7 +5853,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="2:4">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B7" s="5" t="s">
         <v>54</v>
       </c>
@@ -5867,7 +5864,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="2:4">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B8" s="5" t="s">
         <v>56</v>
       </c>
@@ -5878,7 +5875,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="2:4">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B9" s="5" t="s">
         <v>10</v>
       </c>
@@ -5889,7 +5886,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="2:4">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B10" s="5" t="s">
         <v>13</v>
       </c>
@@ -5900,7 +5897,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="2:4">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B11" s="5" t="s">
         <v>61</v>
       </c>
@@ -5911,7 +5908,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="2:4">
+    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B12" s="5" t="s">
         <v>63</v>
       </c>
@@ -5922,12 +5919,12 @@
         <v>64</v>
       </c>
     </row>
-    <row r="14" spans="2:4">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B14" s="24" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="2:4">
+    <row r="15" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B15" s="25" t="s">
         <v>66</v>
       </c>
@@ -5938,7 +5935,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="2:4">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B16" s="26">
         <v>46307</v>
       </c>
@@ -5949,7 +5946,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="2:5">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" s="26">
         <v>46328</v>
       </c>
@@ -5960,7 +5957,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="18" spans="2:5">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" s="26">
         <v>46342</v>
       </c>
@@ -5971,50 +5968,50 @@
         <v>72</v>
       </c>
     </row>
-    <row r="21" spans="2:5">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" s="24" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="22" spans="2:5">
-      <c r="B22" s="161" t="s">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="160" t="s">
         <v>74</v>
       </c>
-      <c r="C22" s="161"/>
-      <c r="D22" s="161"/>
-      <c r="E22" s="161"/>
-    </row>
-    <row r="23" spans="2:5">
-      <c r="B23" s="161" t="s">
+      <c r="C22" s="160"/>
+      <c r="D22" s="160"/>
+      <c r="E22" s="160"/>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B23" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="C23" s="161"/>
-      <c r="D23" s="161"/>
-      <c r="E23" s="161"/>
-    </row>
-    <row r="24" spans="2:5">
-      <c r="B24" s="161" t="s">
+      <c r="C23" s="160"/>
+      <c r="D23" s="160"/>
+      <c r="E23" s="160"/>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B24" s="160" t="s">
         <v>76</v>
       </c>
-      <c r="C24" s="161"/>
-      <c r="D24" s="161"/>
-      <c r="E24" s="161"/>
-    </row>
-    <row r="25" spans="2:5">
-      <c r="B25" s="161" t="s">
+      <c r="C24" s="160"/>
+      <c r="D24" s="160"/>
+      <c r="E24" s="160"/>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B25" s="160" t="s">
         <v>77</v>
       </c>
-      <c r="C25" s="161"/>
-      <c r="D25" s="161"/>
-      <c r="E25" s="161"/>
-    </row>
-    <row r="26" spans="2:5">
-      <c r="B26" s="161" t="s">
+      <c r="C25" s="160"/>
+      <c r="D25" s="160"/>
+      <c r="E25" s="160"/>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B26" s="160" t="s">
         <v>78</v>
       </c>
-      <c r="C26" s="161"/>
-      <c r="D26" s="161"/>
-      <c r="E26" s="161"/>
+      <c r="C26" s="160"/>
+      <c r="D26" s="160"/>
+      <c r="E26" s="160"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -6032,7 +6029,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J129"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5546875" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -6044,7 +6041,7 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="21.75" customHeight="1">
+    <row r="1" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="27" t="s">
         <v>66</v>
       </c>
@@ -6076,7 +6073,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="26">
         <v>46281</v>
       </c>
@@ -6109,7 +6106,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="26">
         <v>46281</v>
       </c>
@@ -6140,7 +6137,7 @@
       </c>
       <c r="J3" s="5"/>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="26">
         <v>46282</v>
       </c>
@@ -6171,7 +6168,7 @@
       </c>
       <c r="J4" s="5"/>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="26">
         <v>46282</v>
       </c>
@@ -6202,7 +6199,7 @@
       </c>
       <c r="J5" s="5"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="26">
         <v>46283</v>
       </c>
@@ -6233,7 +6230,7 @@
       </c>
       <c r="J6" s="5"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="26">
         <v>46283</v>
       </c>
@@ -6264,7 +6261,7 @@
       </c>
       <c r="J7" s="5"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="26">
         <v>46286</v>
       </c>
@@ -6295,7 +6292,7 @@
       </c>
       <c r="J8" s="5"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="26">
         <v>46286</v>
       </c>
@@ -6326,7 +6323,7 @@
       </c>
       <c r="J9" s="5"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="26">
         <v>46287</v>
       </c>
@@ -6357,7 +6354,7 @@
       </c>
       <c r="J10" s="5"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="26">
         <v>46287</v>
       </c>
@@ -6388,7 +6385,7 @@
       </c>
       <c r="J11" s="5"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="26">
         <v>46288</v>
       </c>
@@ -6419,7 +6416,7 @@
       </c>
       <c r="J12" s="5"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="26">
         <v>46288</v>
       </c>
@@ -6450,7 +6447,7 @@
       </c>
       <c r="J13" s="5"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="26">
         <v>46289</v>
       </c>
@@ -6481,7 +6478,7 @@
       </c>
       <c r="J14" s="5"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="26">
         <v>46289</v>
       </c>
@@ -6512,7 +6509,7 @@
       </c>
       <c r="J15" s="5"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="26">
         <v>46289</v>
       </c>
@@ -6543,7 +6540,7 @@
       </c>
       <c r="J16" s="5"/>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="26">
         <v>46289</v>
       </c>
@@ -6574,7 +6571,7 @@
       </c>
       <c r="J17" s="5"/>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="26">
         <v>46290</v>
       </c>
@@ -6605,7 +6602,7 @@
       </c>
       <c r="J18" s="5"/>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="26">
         <v>46290</v>
       </c>
@@ -6636,7 +6633,7 @@
       </c>
       <c r="J19" s="5"/>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="26">
         <v>46293</v>
       </c>
@@ -6667,7 +6664,7 @@
       </c>
       <c r="J20" s="5"/>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="26">
         <v>46293</v>
       </c>
@@ -6698,7 +6695,7 @@
       </c>
       <c r="J21" s="5"/>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="26">
         <v>46294</v>
       </c>
@@ -6729,7 +6726,7 @@
       </c>
       <c r="J22" s="5"/>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="26">
         <v>46294</v>
       </c>
@@ -6760,7 +6757,7 @@
       </c>
       <c r="J23" s="5"/>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="26">
         <v>46295</v>
       </c>
@@ -6791,7 +6788,7 @@
       </c>
       <c r="J24" s="5"/>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="26">
         <v>46295</v>
       </c>
@@ -6822,7 +6819,7 @@
       </c>
       <c r="J25" s="5"/>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="26">
         <v>46296</v>
       </c>
@@ -6853,7 +6850,7 @@
       </c>
       <c r="J26" s="5"/>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="26">
         <v>46296</v>
       </c>
@@ -6884,7 +6881,7 @@
       </c>
       <c r="J27" s="5"/>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="26">
         <v>46296</v>
       </c>
@@ -6915,7 +6912,7 @@
       </c>
       <c r="J28" s="5"/>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="26">
         <v>46296</v>
       </c>
@@ -6946,7 +6943,7 @@
       </c>
       <c r="J29" s="5"/>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="26">
         <v>46297</v>
       </c>
@@ -6977,7 +6974,7 @@
       </c>
       <c r="J30" s="5"/>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="26">
         <v>46297</v>
       </c>
@@ -7008,7 +7005,7 @@
       </c>
       <c r="J31" s="5"/>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="26">
         <v>46300</v>
       </c>
@@ -7039,7 +7036,7 @@
       </c>
       <c r="J32" s="5"/>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="26">
         <v>46300</v>
       </c>
@@ -7070,7 +7067,7 @@
       </c>
       <c r="J33" s="5"/>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="26">
         <v>46301</v>
       </c>
@@ -7101,7 +7098,7 @@
       </c>
       <c r="J34" s="5"/>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="26">
         <v>46301</v>
       </c>
@@ -7132,7 +7129,7 @@
       </c>
       <c r="J35" s="5"/>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="26">
         <v>46302</v>
       </c>
@@ -7163,7 +7160,7 @@
       </c>
       <c r="J36" s="5"/>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="26">
         <v>46302</v>
       </c>
@@ -7194,7 +7191,7 @@
       </c>
       <c r="J37" s="5"/>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="26">
         <v>46303</v>
       </c>
@@ -7225,7 +7222,7 @@
       </c>
       <c r="J38" s="5"/>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="26">
         <v>46303</v>
       </c>
@@ -7256,7 +7253,7 @@
       </c>
       <c r="J39" s="5"/>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="26">
         <v>46303</v>
       </c>
@@ -7287,7 +7284,7 @@
       </c>
       <c r="J40" s="5"/>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="26">
         <v>46303</v>
       </c>
@@ -7318,7 +7315,7 @@
       </c>
       <c r="J41" s="5"/>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="26">
         <v>46304</v>
       </c>
@@ -7347,7 +7344,7 @@
       </c>
       <c r="J42" s="5"/>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="26">
         <v>46304</v>
       </c>
@@ -7376,7 +7373,7 @@
       </c>
       <c r="J43" s="5"/>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="26">
         <v>46308</v>
       </c>
@@ -7405,7 +7402,7 @@
       </c>
       <c r="J44" s="5"/>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="26">
         <v>46308</v>
       </c>
@@ -7434,7 +7431,7 @@
       </c>
       <c r="J45" s="5"/>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="26">
         <v>46309</v>
       </c>
@@ -7463,7 +7460,7 @@
       </c>
       <c r="J46" s="5"/>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="26">
         <v>46309</v>
       </c>
@@ -7492,7 +7489,7 @@
       </c>
       <c r="J47" s="5"/>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="26">
         <v>46310</v>
       </c>
@@ -7521,7 +7518,7 @@
       </c>
       <c r="J48" s="5"/>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="26">
         <v>46310</v>
       </c>
@@ -7550,7 +7547,7 @@
       </c>
       <c r="J49" s="5"/>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="26">
         <v>46311</v>
       </c>
@@ -7579,7 +7576,7 @@
       </c>
       <c r="J50" s="5"/>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="26">
         <v>46311</v>
       </c>
@@ -7608,7 +7605,7 @@
       </c>
       <c r="J51" s="5"/>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="26">
         <v>46314</v>
       </c>
@@ -7637,7 +7634,7 @@
       </c>
       <c r="J52" s="5"/>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="26">
         <v>46314</v>
       </c>
@@ -7666,7 +7663,7 @@
       </c>
       <c r="J53" s="5"/>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="26">
         <v>46315</v>
       </c>
@@ -7695,7 +7692,7 @@
       </c>
       <c r="J54" s="5"/>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="26">
         <v>46315</v>
       </c>
@@ -7724,7 +7721,7 @@
       </c>
       <c r="J55" s="5"/>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="26">
         <v>46316</v>
       </c>
@@ -7753,7 +7750,7 @@
       </c>
       <c r="J56" s="5"/>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="26">
         <v>46316</v>
       </c>
@@ -7782,7 +7779,7 @@
       </c>
       <c r="J57" s="5"/>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="26">
         <v>46316</v>
       </c>
@@ -7811,7 +7808,7 @@
       </c>
       <c r="J58" s="5"/>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="26">
         <v>46316</v>
       </c>
@@ -7840,7 +7837,7 @@
       </c>
       <c r="J59" s="5"/>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="26">
         <v>46317</v>
       </c>
@@ -7869,7 +7866,7 @@
       </c>
       <c r="J60" s="5"/>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="26">
         <v>46317</v>
       </c>
@@ -7898,7 +7895,7 @@
       </c>
       <c r="J61" s="5"/>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="26">
         <v>46318</v>
       </c>
@@ -7927,7 +7924,7 @@
       </c>
       <c r="J62" s="5"/>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="26">
         <v>46318</v>
       </c>
@@ -7956,7 +7953,7 @@
       </c>
       <c r="J63" s="5"/>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="26">
         <v>46321</v>
       </c>
@@ -7985,7 +7982,7 @@
       </c>
       <c r="J64" s="5"/>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="26">
         <v>46321</v>
       </c>
@@ -8014,7 +8011,7 @@
       </c>
       <c r="J65" s="5"/>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="26">
         <v>46321</v>
       </c>
@@ -8043,7 +8040,7 @@
       </c>
       <c r="J66" s="5"/>
     </row>
-    <row r="67" spans="1:10">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="26">
         <v>46321</v>
       </c>
@@ -8072,7 +8069,7 @@
       </c>
       <c r="J67" s="5"/>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="26">
         <v>46322</v>
       </c>
@@ -8101,7 +8098,7 @@
       </c>
       <c r="J68" s="5"/>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="26">
         <v>46322</v>
       </c>
@@ -8130,7 +8127,7 @@
       </c>
       <c r="J69" s="5"/>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="26">
         <v>46323</v>
       </c>
@@ -8159,7 +8156,7 @@
       </c>
       <c r="J70" s="5"/>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="26">
         <v>46323</v>
       </c>
@@ -8188,7 +8185,7 @@
       </c>
       <c r="J71" s="5"/>
     </row>
-    <row r="72" spans="1:10">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="26">
         <v>46323</v>
       </c>
@@ -8217,7 +8214,7 @@
       </c>
       <c r="J72" s="5"/>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="26">
         <v>46323</v>
       </c>
@@ -8246,7 +8243,7 @@
       </c>
       <c r="J73" s="5"/>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="26">
         <v>46324</v>
       </c>
@@ -8275,7 +8272,7 @@
       </c>
       <c r="J74" s="5"/>
     </row>
-    <row r="75" spans="1:10">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="26">
         <v>46324</v>
       </c>
@@ -8304,7 +8301,7 @@
       </c>
       <c r="J75" s="5"/>
     </row>
-    <row r="76" spans="1:10">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="26">
         <v>46325</v>
       </c>
@@ -8333,7 +8330,7 @@
       </c>
       <c r="J76" s="5"/>
     </row>
-    <row r="77" spans="1:10">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" s="26">
         <v>46325</v>
       </c>
@@ -8362,7 +8359,7 @@
       </c>
       <c r="J77" s="5"/>
     </row>
-    <row r="78" spans="1:10">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="26">
         <v>46329</v>
       </c>
@@ -8391,7 +8388,7 @@
       </c>
       <c r="J78" s="5"/>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="26">
         <v>46329</v>
       </c>
@@ -8420,7 +8417,7 @@
       </c>
       <c r="J79" s="5"/>
     </row>
-    <row r="80" spans="1:10">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="26">
         <v>46330</v>
       </c>
@@ -8449,7 +8446,7 @@
       </c>
       <c r="J80" s="5"/>
     </row>
-    <row r="81" spans="1:10">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="26">
         <v>46330</v>
       </c>
@@ -8478,7 +8475,7 @@
       </c>
       <c r="J81" s="5"/>
     </row>
-    <row r="82" spans="1:10">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="26">
         <v>46331</v>
       </c>
@@ -8507,7 +8504,7 @@
       </c>
       <c r="J82" s="5"/>
     </row>
-    <row r="83" spans="1:10">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="26">
         <v>46331</v>
       </c>
@@ -8536,7 +8533,7 @@
       </c>
       <c r="J83" s="5"/>
     </row>
-    <row r="84" spans="1:10">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" s="26">
         <v>46331</v>
       </c>
@@ -8565,7 +8562,7 @@
       </c>
       <c r="J84" s="5"/>
     </row>
-    <row r="85" spans="1:10">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="26">
         <v>46331</v>
       </c>
@@ -8594,7 +8591,7 @@
       </c>
       <c r="J85" s="5"/>
     </row>
-    <row r="86" spans="1:10">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" s="26">
         <v>46332</v>
       </c>
@@ -8623,7 +8620,7 @@
       </c>
       <c r="J86" s="5"/>
     </row>
-    <row r="87" spans="1:10">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="26">
         <v>46332</v>
       </c>
@@ -8652,7 +8649,7 @@
       </c>
       <c r="J87" s="5"/>
     </row>
-    <row r="88" spans="1:10">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" s="26">
         <v>46335</v>
       </c>
@@ -8681,7 +8678,7 @@
       </c>
       <c r="J88" s="5"/>
     </row>
-    <row r="89" spans="1:10">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="26">
         <v>46335</v>
       </c>
@@ -8710,7 +8707,7 @@
       </c>
       <c r="J89" s="5"/>
     </row>
-    <row r="90" spans="1:10">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" s="26">
         <v>46335</v>
       </c>
@@ -8739,7 +8736,7 @@
       </c>
       <c r="J90" s="5"/>
     </row>
-    <row r="91" spans="1:10">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" s="26">
         <v>46335</v>
       </c>
@@ -8768,7 +8765,7 @@
       </c>
       <c r="J91" s="5"/>
     </row>
-    <row r="92" spans="1:10">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" s="26">
         <v>46336</v>
       </c>
@@ -8797,7 +8794,7 @@
       </c>
       <c r="J92" s="5"/>
     </row>
-    <row r="93" spans="1:10">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" s="26">
         <v>46336</v>
       </c>
@@ -8826,7 +8823,7 @@
       </c>
       <c r="J93" s="5"/>
     </row>
-    <row r="94" spans="1:10">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" s="26">
         <v>46337</v>
       </c>
@@ -8855,7 +8852,7 @@
       </c>
       <c r="J94" s="5"/>
     </row>
-    <row r="95" spans="1:10">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="26">
         <v>46337</v>
       </c>
@@ -8884,7 +8881,7 @@
       </c>
       <c r="J95" s="5"/>
     </row>
-    <row r="96" spans="1:10">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" s="26">
         <v>46337</v>
       </c>
@@ -8913,7 +8910,7 @@
       </c>
       <c r="J96" s="5"/>
     </row>
-    <row r="97" spans="1:10">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" s="26">
         <v>46337</v>
       </c>
@@ -8942,7 +8939,7 @@
       </c>
       <c r="J97" s="5"/>
     </row>
-    <row r="98" spans="1:10">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" s="26">
         <v>46338</v>
       </c>
@@ -8971,7 +8968,7 @@
       </c>
       <c r="J98" s="5"/>
     </row>
-    <row r="99" spans="1:10">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" s="26">
         <v>46338</v>
       </c>
@@ -9000,7 +8997,7 @@
       </c>
       <c r="J99" s="5"/>
     </row>
-    <row r="100" spans="1:10">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" s="26">
         <v>46339</v>
       </c>
@@ -9029,7 +9026,7 @@
       </c>
       <c r="J100" s="5"/>
     </row>
-    <row r="101" spans="1:10">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" s="26">
         <v>46339</v>
       </c>
@@ -9058,7 +9055,7 @@
       </c>
       <c r="J101" s="5"/>
     </row>
-    <row r="102" spans="1:10">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" s="26">
         <v>46343</v>
       </c>
@@ -9087,7 +9084,7 @@
       </c>
       <c r="J102" s="5"/>
     </row>
-    <row r="103" spans="1:10">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" s="26">
         <v>46343</v>
       </c>
@@ -9116,7 +9113,7 @@
       </c>
       <c r="J103" s="5"/>
     </row>
-    <row r="104" spans="1:10">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" s="26">
         <v>46344</v>
       </c>
@@ -9145,7 +9142,7 @@
       </c>
       <c r="J104" s="5"/>
     </row>
-    <row r="105" spans="1:10">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" s="26">
         <v>46344</v>
       </c>
@@ -9174,7 +9171,7 @@
       </c>
       <c r="J105" s="5"/>
     </row>
-    <row r="106" spans="1:10">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" s="26">
         <v>46345</v>
       </c>
@@ -9203,7 +9200,7 @@
       </c>
       <c r="J106" s="5"/>
     </row>
-    <row r="107" spans="1:10">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" s="26">
         <v>46345</v>
       </c>
@@ -9232,7 +9229,7 @@
       </c>
       <c r="J107" s="5"/>
     </row>
-    <row r="108" spans="1:10">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" s="26">
         <v>46346</v>
       </c>
@@ -9261,7 +9258,7 @@
       </c>
       <c r="J108" s="5"/>
     </row>
-    <row r="109" spans="1:10">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" s="26">
         <v>46346</v>
       </c>
@@ -9290,7 +9287,7 @@
       </c>
       <c r="J109" s="5"/>
     </row>
-    <row r="110" spans="1:10">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" s="26">
         <v>46346</v>
       </c>
@@ -9319,7 +9316,7 @@
       </c>
       <c r="J110" s="5"/>
     </row>
-    <row r="111" spans="1:10">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" s="26">
         <v>46346</v>
       </c>
@@ -9348,7 +9345,7 @@
       </c>
       <c r="J111" s="5"/>
     </row>
-    <row r="112" spans="1:10">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" s="26">
         <v>46349</v>
       </c>
@@ -9377,7 +9374,7 @@
       </c>
       <c r="J112" s="5"/>
     </row>
-    <row r="113" spans="1:10">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" s="26">
         <v>46349</v>
       </c>
@@ -9406,7 +9403,7 @@
       </c>
       <c r="J113" s="5"/>
     </row>
-    <row r="114" spans="1:10">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" s="26">
         <v>46350</v>
       </c>
@@ -9435,7 +9432,7 @@
       </c>
       <c r="J114" s="5"/>
     </row>
-    <row r="115" spans="1:10">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" s="26">
         <v>46350</v>
       </c>
@@ -9464,7 +9461,7 @@
       </c>
       <c r="J115" s="5"/>
     </row>
-    <row r="116" spans="1:10">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" s="26">
         <v>46350</v>
       </c>
@@ -9493,7 +9490,7 @@
       </c>
       <c r="J116" s="5"/>
     </row>
-    <row r="117" spans="1:10">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" s="26">
         <v>46350</v>
       </c>
@@ -9522,7 +9519,7 @@
       </c>
       <c r="J117" s="5"/>
     </row>
-    <row r="118" spans="1:10">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" s="26">
         <v>46351</v>
       </c>
@@ -9551,7 +9548,7 @@
       </c>
       <c r="J118" s="5"/>
     </row>
-    <row r="119" spans="1:10">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" s="26">
         <v>46351</v>
       </c>
@@ -9580,7 +9577,7 @@
       </c>
       <c r="J119" s="5"/>
     </row>
-    <row r="120" spans="1:10">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" s="26">
         <v>46352</v>
       </c>
@@ -9609,7 +9606,7 @@
       </c>
       <c r="J120" s="5"/>
     </row>
-    <row r="121" spans="1:10">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" s="26">
         <v>46352</v>
       </c>
@@ -9638,7 +9635,7 @@
       </c>
       <c r="J121" s="5"/>
     </row>
-    <row r="122" spans="1:10">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" s="26">
         <v>46352</v>
       </c>
@@ -9667,7 +9664,7 @@
       </c>
       <c r="J122" s="5"/>
     </row>
-    <row r="123" spans="1:10">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" s="26">
         <v>46352</v>
       </c>
@@ -9696,7 +9693,7 @@
       </c>
       <c r="J123" s="5"/>
     </row>
-    <row r="124" spans="1:10">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" s="26">
         <v>46353</v>
       </c>
@@ -9725,7 +9722,7 @@
       </c>
       <c r="J124" s="5"/>
     </row>
-    <row r="125" spans="1:10">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" s="26">
         <v>46353</v>
       </c>
@@ -9754,7 +9751,7 @@
       </c>
       <c r="J125" s="5"/>
     </row>
-    <row r="126" spans="1:10">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" s="26">
         <v>46356</v>
       </c>
@@ -9783,7 +9780,7 @@
       </c>
       <c r="J126" s="5"/>
     </row>
-    <row r="127" spans="1:10">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" s="26">
         <v>46356</v>
       </c>
@@ -9812,7 +9809,7 @@
       </c>
       <c r="J127" s="5"/>
     </row>
-    <row r="129" spans="6:9">
+    <row r="129" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F129" s="34" t="s">
         <v>36</v>
       </c>
@@ -9848,7 +9845,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:J12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5546875" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -9858,12 +9855,12 @@
     <col min="6" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" ht="16.8">
+    <row r="2" spans="2:10" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B2" s="21" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="3" spans="2:10">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>21</v>
       </c>
@@ -9892,7 +9889,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" s="10" t="s">
         <v>28</v>
       </c>
@@ -9921,7 +9918,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B5" s="10" t="s">
         <v>28</v>
       </c>
@@ -9950,7 +9947,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="2:10">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" s="10" t="s">
         <v>30</v>
       </c>
@@ -9979,7 +9976,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:10">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" s="10" t="s">
         <v>30</v>
       </c>
@@ -10008,7 +10005,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="2:10">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="10" t="s">
         <v>32</v>
       </c>
@@ -10037,7 +10034,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="2:10">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
         <v>32</v>
       </c>
@@ -10066,7 +10063,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="2:10">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="10" t="s">
         <v>34</v>
       </c>
@@ -10095,7 +10092,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="2:10">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="10" t="s">
         <v>34</v>
       </c>
@@ -10124,7 +10121,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="2:10">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="13" t="s">
         <v>36</v>
       </c>
@@ -10149,7 +10146,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:I57"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5546875" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
@@ -10158,7 +10155,7 @@
     <col min="9" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="35" t="s">
         <v>66</v>
       </c>
@@ -10187,7 +10184,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="26">
         <v>46281</v>
       </c>
@@ -10219,7 +10216,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="26">
         <v>46282</v>
       </c>
@@ -10251,7 +10248,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="26">
         <v>46283</v>
       </c>
@@ -10283,7 +10280,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="26">
         <v>46286</v>
       </c>
@@ -10315,7 +10312,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="26">
         <v>46287</v>
       </c>
@@ -10347,7 +10344,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="26">
         <v>46288</v>
       </c>
@@ -10379,7 +10376,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="26">
         <v>46289</v>
       </c>
@@ -10411,7 +10408,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="26">
         <v>46290</v>
       </c>
@@ -10443,7 +10440,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="26">
         <v>46293</v>
       </c>
@@ -10475,7 +10472,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="26">
         <v>46294</v>
       </c>
@@ -10507,7 +10504,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="26">
         <v>46295</v>
       </c>
@@ -10539,7 +10536,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="26">
         <v>46296</v>
       </c>
@@ -10571,7 +10568,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="26">
         <v>46297</v>
       </c>
@@ -10603,7 +10600,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="26">
         <v>46300</v>
       </c>
@@ -10635,7 +10632,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="26">
         <v>46301</v>
       </c>
@@ -10667,7 +10664,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="26">
         <v>46302</v>
       </c>
@@ -10699,7 +10696,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="26">
         <v>46303</v>
       </c>
@@ -10731,7 +10728,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="26">
         <v>46304</v>
       </c>
@@ -10763,7 +10760,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="26">
         <v>46307</v>
       </c>
@@ -10797,7 +10794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="26">
         <v>46308</v>
       </c>
@@ -10829,7 +10826,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="26">
         <v>46309</v>
       </c>
@@ -10861,7 +10858,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="26">
         <v>46310</v>
       </c>
@@ -10893,7 +10890,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="26">
         <v>46311</v>
       </c>
@@ -10925,7 +10922,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="26">
         <v>46314</v>
       </c>
@@ -10957,7 +10954,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="26">
         <v>46315</v>
       </c>
@@ -10989,7 +10986,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="26">
         <v>46316</v>
       </c>
@@ -11021,7 +11018,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="26">
         <v>46317</v>
       </c>
@@ -11053,7 +11050,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="26">
         <v>46318</v>
       </c>
@@ -11085,7 +11082,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="26">
         <v>46321</v>
       </c>
@@ -11117,7 +11114,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="26">
         <v>46322</v>
       </c>
@@ -11149,7 +11146,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="26">
         <v>46323</v>
       </c>
@@ -11181,7 +11178,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="26">
         <v>46324</v>
       </c>
@@ -11213,7 +11210,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="26">
         <v>46325</v>
       </c>
@@ -11245,7 +11242,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="26">
         <v>46328</v>
       </c>
@@ -11279,7 +11276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="26">
         <v>46329</v>
       </c>
@@ -11311,7 +11308,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="26">
         <v>46330</v>
       </c>
@@ -11343,7 +11340,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="26">
         <v>46331</v>
       </c>
@@ -11375,7 +11372,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="26">
         <v>46332</v>
       </c>
@@ -11407,7 +11404,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="26">
         <v>46335</v>
       </c>
@@ -11439,7 +11436,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="26">
         <v>46336</v>
       </c>
@@ -11471,7 +11468,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="26">
         <v>46337</v>
       </c>
@@ -11503,7 +11500,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="26">
         <v>46338</v>
       </c>
@@ -11535,7 +11532,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="26">
         <v>46339</v>
       </c>
@@ -11567,7 +11564,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="26">
         <v>46342</v>
       </c>
@@ -11601,7 +11598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="26">
         <v>46343</v>
       </c>
@@ -11633,7 +11630,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="26">
         <v>46344</v>
       </c>
@@ -11665,7 +11662,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="26">
         <v>46345</v>
       </c>
@@ -11697,7 +11694,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="26">
         <v>46346</v>
       </c>
@@ -11729,7 +11726,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="26">
         <v>46349</v>
       </c>
@@ -11761,7 +11758,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="26">
         <v>46350</v>
       </c>
@@ -11793,7 +11790,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="26">
         <v>46351</v>
       </c>
@@ -11825,7 +11822,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="26">
         <v>46352</v>
       </c>
@@ -11857,7 +11854,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="26">
         <v>46353</v>
       </c>
@@ -11889,7 +11886,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="26">
         <v>46356</v>
       </c>
@@ -11921,7 +11918,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C57" s="24" t="s">
         <v>36</v>
       </c>
@@ -11965,18 +11962,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D54"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5546875" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="4" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.8">
+    <row r="1" spans="1:4" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="35" t="s">
         <v>66</v>
       </c>
@@ -11990,7 +11987,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="39">
         <v>46281</v>
       </c>
@@ -12007,7 +12004,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="39">
         <v>46282</v>
       </c>
@@ -12024,7 +12021,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>46283</v>
       </c>
@@ -12041,7 +12038,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="39">
         <v>46286</v>
       </c>
@@ -12058,7 +12055,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <v>46287</v>
       </c>
@@ -12075,7 +12072,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="39">
         <v>46288</v>
       </c>
@@ -12092,7 +12089,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <v>46289</v>
       </c>
@@ -12109,7 +12106,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="39">
         <v>46290</v>
       </c>
@@ -12126,7 +12123,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="39">
         <v>46293</v>
       </c>
@@ -12143,7 +12140,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="39">
         <v>46294</v>
       </c>
@@ -12160,7 +12157,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="39">
         <v>46295</v>
       </c>
@@ -12177,7 +12174,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="39">
         <v>46296</v>
       </c>
@@ -12194,7 +12191,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <v>46297</v>
       </c>
@@ -12211,7 +12208,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="39">
         <v>46300</v>
       </c>
@@ -12228,7 +12225,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="39">
         <v>46301</v>
       </c>
@@ -12245,7 +12242,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="39">
         <v>46302</v>
       </c>
@@ -12262,7 +12259,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="39">
         <v>46303</v>
       </c>
@@ -12279,7 +12276,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="39">
         <v>46304</v>
       </c>
@@ -12296,7 +12293,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="39">
         <v>46308</v>
       </c>
@@ -12313,7 +12310,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="39">
         <v>46309</v>
       </c>
@@ -12330,7 +12327,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="39">
         <v>46310</v>
       </c>
@@ -12347,7 +12344,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="39">
         <v>46311</v>
       </c>
@@ -12364,7 +12361,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="39">
         <v>46314</v>
       </c>
@@ -12381,7 +12378,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="39">
         <v>46315</v>
       </c>
@@ -12398,7 +12395,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="39">
         <v>46316</v>
       </c>
@@ -12415,7 +12412,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="39">
         <v>46317</v>
       </c>
@@ -12432,7 +12429,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="39">
         <v>46318</v>
       </c>
@@ -12449,7 +12446,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="39">
         <v>46321</v>
       </c>
@@ -12466,7 +12463,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="39">
         <v>46322</v>
       </c>
@@ -12483,7 +12480,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="39">
         <v>46323</v>
       </c>
@@ -12500,7 +12497,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="39">
         <v>46324</v>
       </c>
@@ -12517,7 +12514,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="39">
         <v>46325</v>
       </c>
@@ -12534,7 +12531,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="39">
         <v>46329</v>
       </c>
@@ -12551,7 +12548,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="39">
         <v>46330</v>
       </c>
@@ -12568,7 +12565,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="39">
         <v>46331</v>
       </c>
@@ -12585,7 +12582,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="39">
         <v>46332</v>
       </c>
@@ -12602,7 +12599,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="39">
         <v>46335</v>
       </c>
@@ -12619,7 +12616,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="39">
         <v>46336</v>
       </c>
@@ -12636,7 +12633,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="39">
         <v>46337</v>
       </c>
@@ -12653,7 +12650,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="39">
         <v>46338</v>
       </c>
@@ -12670,7 +12667,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="39">
         <v>46339</v>
       </c>
@@ -12687,7 +12684,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="39">
         <v>46343</v>
       </c>
@@ -12704,7 +12701,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="39">
         <v>46344</v>
       </c>
@@ -12721,7 +12718,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="39">
         <v>46345</v>
       </c>
@@ -12738,7 +12735,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="39">
         <v>46346</v>
       </c>
@@ -12755,7 +12752,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="39">
         <v>46349</v>
       </c>
@@ -12772,7 +12769,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="39">
         <v>46350</v>
       </c>
@@ -12789,7 +12786,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="39">
         <v>46351</v>
       </c>
@@ -12806,7 +12803,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="39">
         <v>46352</v>
       </c>
@@ -12823,7 +12820,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="39">
         <v>46353</v>
       </c>
@@ -12840,7 +12837,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="39">
         <v>46356</v>
       </c>
@@ -12867,7 +12864,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56610E24-BD28-4180-A9FE-3618B3866E11}">
   <dimension ref="A1:H149"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="65.6640625" defaultRowHeight="24.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="65.6640625" defaultRowHeight="24.75" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="84" style="40" customWidth="1"/>
     <col min="2" max="2" width="65.6640625" style="40"/>
@@ -12875,7 +12872,7 @@
     <col min="4" max="16384" width="65.6640625" style="40"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="24.75" customHeight="1">
+    <row r="1" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="43"/>
       <c r="B1" s="44" t="s">
         <v>24</v>
@@ -12889,53 +12886,56 @@
       <c r="E1" s="41" t="s">
         <v>119</v>
       </c>
-      <c r="F1" s="135" t="s">
+      <c r="F1" s="134" t="s">
         <v>120</v>
       </c>
-      <c r="G1" s="143" t="s">
+      <c r="G1" s="142" t="s">
         <v>271</v>
       </c>
-      <c r="H1" s="140" t="s">
+      <c r="H1" s="139" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="24.75" customHeight="1">
+    <row r="2" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="47" t="s">
         <v>122</v>
       </c>
-      <c r="B2" s="156">
+      <c r="B2" s="155">
         <f>COUNTA(B4:C38,B40:C82,B84:C94,B96:C141,B143:C149)</f>
         <v>112</v>
       </c>
-      <c r="C2" s="156"/>
+      <c r="C2" s="155"/>
       <c r="D2" s="48"/>
       <c r="E2" s="42">
         <f>COUNTA(E4:E30,E40:E68,E84:E90)</f>
         <v>47</v>
       </c>
-      <c r="F2" s="133"/>
-      <c r="G2" s="150">
+      <c r="F2" s="42">
+        <f>COUNTA(F4:F30,F40:F68,F84:F90)-G2</f>
+        <v>44</v>
+      </c>
+      <c r="G2" s="149">
         <f>COUNTA(G4:G30,G40:G68,G84:G90)</f>
-        <v>0</v>
-      </c>
-      <c r="H2" s="141">
+        <v>3</v>
+      </c>
+      <c r="H2" s="140">
         <f>COUNTA(H4:H30,H40:H68,H84:H90)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A3" s="159" t="s">
+    <row r="3" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="158" t="s">
         <v>123</v>
       </c>
-      <c r="B3" s="160"/>
-      <c r="C3" s="160"/>
-      <c r="D3" s="160"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="160"/>
-      <c r="H3" s="160"/>
-    </row>
-    <row r="4" spans="1:8" ht="24.75" customHeight="1">
+      <c r="B3" s="159"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="159"/>
+      <c r="G3" s="159"/>
+      <c r="H3" s="159"/>
+    </row>
+    <row r="4" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49" t="s">
         <v>124</v>
       </c>
@@ -12949,13 +12949,15 @@
       <c r="E4" s="52" t="s">
         <v>126</v>
       </c>
-      <c r="F4" s="136" t="s">
+      <c r="F4" s="135" t="s">
         <v>127</v>
       </c>
-      <c r="G4" s="146"/>
-      <c r="H4" s="142"/>
-    </row>
-    <row r="5" spans="1:8" ht="24.75" customHeight="1">
+      <c r="G4" s="145" t="s">
+        <v>126</v>
+      </c>
+      <c r="H4" s="141"/>
+    </row>
+    <row r="5" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="54" t="s">
         <v>124</v>
       </c>
@@ -12972,10 +12974,10 @@
       <c r="F5" s="128" t="s">
         <v>129</v>
       </c>
-      <c r="G5" s="144"/>
+      <c r="G5" s="143"/>
       <c r="H5" s="53"/>
     </row>
-    <row r="6" spans="1:8" ht="24.75" customHeight="1">
+    <row r="6" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="49" t="s">
         <v>124</v>
       </c>
@@ -12988,10 +12990,10 @@
       </c>
       <c r="E6" s="52"/>
       <c r="F6" s="128"/>
-      <c r="G6" s="144"/>
+      <c r="G6" s="143"/>
       <c r="H6" s="57"/>
     </row>
-    <row r="7" spans="1:8" ht="24.75" customHeight="1">
+    <row r="7" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>124</v>
       </c>
@@ -13004,10 +13006,10 @@
       </c>
       <c r="E7" s="52"/>
       <c r="F7" s="128"/>
-      <c r="G7" s="144"/>
+      <c r="G7" s="143"/>
       <c r="H7" s="57"/>
     </row>
-    <row r="8" spans="1:8" ht="24.75" customHeight="1">
+    <row r="8" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="60" t="s">
         <v>124</v>
       </c>
@@ -13024,10 +13026,10 @@
       <c r="F8" s="128" t="s">
         <v>133</v>
       </c>
-      <c r="G8" s="144"/>
+      <c r="G8" s="143"/>
       <c r="H8" s="57"/>
     </row>
-    <row r="9" spans="1:8" ht="24.75" customHeight="1">
+    <row r="9" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>124</v>
       </c>
@@ -13044,10 +13046,12 @@
       <c r="F9" s="128" t="s">
         <v>133</v>
       </c>
-      <c r="G9" s="144"/>
+      <c r="G9" s="143" t="s">
+        <v>126</v>
+      </c>
       <c r="H9" s="57"/>
     </row>
-    <row r="10" spans="1:8" ht="24.75" customHeight="1">
+    <row r="10" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="62" t="s">
         <v>124</v>
       </c>
@@ -13060,10 +13064,10 @@
       </c>
       <c r="E10" s="52"/>
       <c r="F10" s="128"/>
-      <c r="G10" s="144"/>
+      <c r="G10" s="143"/>
       <c r="H10" s="57"/>
     </row>
-    <row r="11" spans="1:8" ht="24.75" customHeight="1">
+    <row r="11" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>136</v>
       </c>
@@ -13080,10 +13084,10 @@
       <c r="F11" s="128" t="s">
         <v>133</v>
       </c>
-      <c r="G11" s="144"/>
+      <c r="G11" s="143"/>
       <c r="H11" s="57"/>
     </row>
-    <row r="12" spans="1:8" ht="24.75" customHeight="1">
+    <row r="12" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="60" t="s">
         <v>136</v>
       </c>
@@ -13097,13 +13101,13 @@
       <c r="E12" s="52" t="s">
         <v>126</v>
       </c>
-      <c r="F12" s="137" t="s">
+      <c r="F12" s="136" t="s">
         <v>127</v>
       </c>
-      <c r="G12" s="144"/>
+      <c r="G12" s="143"/>
       <c r="H12" s="57"/>
     </row>
-    <row r="13" spans="1:8" ht="24.75" customHeight="1">
+    <row r="13" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>136</v>
       </c>
@@ -13116,10 +13120,10 @@
       </c>
       <c r="E13" s="52"/>
       <c r="F13" s="128"/>
-      <c r="G13" s="144"/>
+      <c r="G13" s="143"/>
       <c r="H13" s="57"/>
     </row>
-    <row r="14" spans="1:8" ht="24.75" customHeight="1">
+    <row r="14" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="60" t="s">
         <v>136</v>
       </c>
@@ -13132,10 +13136,10 @@
       </c>
       <c r="E14" s="52"/>
       <c r="F14" s="128"/>
-      <c r="G14" s="144"/>
+      <c r="G14" s="143"/>
       <c r="H14" s="57"/>
     </row>
-    <row r="15" spans="1:8" ht="24.75" customHeight="1">
+    <row r="15" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="54" t="s">
         <v>136</v>
       </c>
@@ -13148,10 +13152,10 @@
       </c>
       <c r="E15" s="52"/>
       <c r="F15" s="128"/>
-      <c r="G15" s="144"/>
+      <c r="G15" s="143"/>
       <c r="H15" s="57"/>
     </row>
-    <row r="16" spans="1:8" ht="24.75" customHeight="1">
+    <row r="16" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="49" t="s">
         <v>136</v>
       </c>
@@ -13168,10 +13172,10 @@
       <c r="F16" s="128" t="s">
         <v>133</v>
       </c>
-      <c r="G16" s="144"/>
+      <c r="G16" s="143"/>
       <c r="H16" s="57"/>
     </row>
-    <row r="17" spans="1:8" ht="24.75" customHeight="1">
+    <row r="17" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="67" t="s">
         <v>136</v>
       </c>
@@ -13185,13 +13189,13 @@
       <c r="E17" s="52" t="s">
         <v>126</v>
       </c>
-      <c r="F17" s="137" t="s">
+      <c r="F17" s="136" t="s">
         <v>127</v>
       </c>
-      <c r="G17" s="144"/>
+      <c r="G17" s="143"/>
       <c r="H17" s="57"/>
     </row>
-    <row r="18" spans="1:8" ht="24.75" customHeight="1">
+    <row r="18" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="49" t="s">
         <v>145</v>
       </c>
@@ -13208,10 +13212,10 @@
       <c r="F18" s="128" t="s">
         <v>127</v>
       </c>
-      <c r="G18" s="144"/>
+      <c r="G18" s="143"/>
       <c r="H18" s="57"/>
     </row>
-    <row r="19" spans="1:8" ht="24.75" customHeight="1">
+    <row r="19" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="54" t="s">
         <v>145</v>
       </c>
@@ -13228,10 +13232,10 @@
       <c r="F19" s="128" t="s">
         <v>133</v>
       </c>
-      <c r="G19" s="144"/>
+      <c r="G19" s="143"/>
       <c r="H19" s="57"/>
     </row>
-    <row r="20" spans="1:8" ht="24.75" customHeight="1">
+    <row r="20" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="49" t="s">
         <v>145</v>
       </c>
@@ -13248,10 +13252,10 @@
       <c r="F20" s="128" t="s">
         <v>127</v>
       </c>
-      <c r="G20" s="144"/>
+      <c r="G20" s="143"/>
       <c r="H20" s="57"/>
     </row>
-    <row r="21" spans="1:8" ht="24.75" customHeight="1">
+    <row r="21" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="54" t="s">
         <v>145</v>
       </c>
@@ -13268,10 +13272,10 @@
       <c r="F21" s="128" t="s">
         <v>127</v>
       </c>
-      <c r="G21" s="144"/>
+      <c r="G21" s="143"/>
       <c r="H21" s="57"/>
     </row>
-    <row r="22" spans="1:8" ht="24.75" customHeight="1">
+    <row r="22" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="49" t="s">
         <v>145</v>
       </c>
@@ -13288,10 +13292,10 @@
       <c r="F22" s="128" t="s">
         <v>129</v>
       </c>
-      <c r="G22" s="144"/>
+      <c r="G22" s="143"/>
       <c r="H22" s="57"/>
     </row>
-    <row r="23" spans="1:8" ht="24.75" customHeight="1">
+    <row r="23" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="54" t="s">
         <v>145</v>
       </c>
@@ -13308,10 +13312,10 @@
       <c r="F23" s="128" t="s">
         <v>129</v>
       </c>
-      <c r="G23" s="144"/>
+      <c r="G23" s="143"/>
       <c r="H23" s="57"/>
     </row>
-    <row r="24" spans="1:8" ht="24.75" customHeight="1">
+    <row r="24" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="70" t="s">
         <v>145</v>
       </c>
@@ -13328,10 +13332,10 @@
       <c r="F24" s="128" t="s">
         <v>127</v>
       </c>
-      <c r="G24" s="144"/>
+      <c r="G24" s="143"/>
       <c r="H24" s="57"/>
     </row>
-    <row r="25" spans="1:8" ht="24.75" customHeight="1">
+    <row r="25" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="54" t="s">
         <v>153</v>
       </c>
@@ -13344,10 +13348,10 @@
       </c>
       <c r="E25" s="52"/>
       <c r="F25" s="128"/>
-      <c r="G25" s="144"/>
+      <c r="G25" s="143"/>
       <c r="H25" s="57"/>
     </row>
-    <row r="26" spans="1:8" ht="24.75" customHeight="1">
+    <row r="26" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="49" t="s">
         <v>153</v>
       </c>
@@ -13364,10 +13368,10 @@
       <c r="F26" s="128" t="s">
         <v>133</v>
       </c>
-      <c r="G26" s="144"/>
+      <c r="G26" s="143"/>
       <c r="H26" s="57"/>
     </row>
-    <row r="27" spans="1:8" ht="24.75" customHeight="1">
+    <row r="27" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="54" t="s">
         <v>153</v>
       </c>
@@ -13384,10 +13388,10 @@
       <c r="F27" s="128" t="s">
         <v>133</v>
       </c>
-      <c r="G27" s="144"/>
+      <c r="G27" s="143"/>
       <c r="H27" s="57"/>
     </row>
-    <row r="28" spans="1:8" ht="24.75" customHeight="1">
+    <row r="28" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="49" t="s">
         <v>153</v>
       </c>
@@ -13400,10 +13404,10 @@
       </c>
       <c r="E28" s="52"/>
       <c r="F28" s="128"/>
-      <c r="G28" s="144"/>
+      <c r="G28" s="143"/>
       <c r="H28" s="57"/>
     </row>
-    <row r="29" spans="1:8" ht="24.75" customHeight="1">
+    <row r="29" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="54" t="s">
         <v>153</v>
       </c>
@@ -13416,10 +13420,10 @@
       </c>
       <c r="E29" s="52"/>
       <c r="F29" s="128"/>
-      <c r="G29" s="144"/>
+      <c r="G29" s="143"/>
       <c r="H29" s="57"/>
     </row>
-    <row r="30" spans="1:8" ht="24.75" customHeight="1">
+    <row r="30" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="72" t="s">
         <v>153</v>
       </c>
@@ -13436,10 +13440,10 @@
       <c r="F30" s="92" t="s">
         <v>133</v>
       </c>
-      <c r="G30" s="144"/>
+      <c r="G30" s="143"/>
       <c r="H30" s="73"/>
     </row>
-    <row r="31" spans="1:8" ht="24.75" customHeight="1">
+    <row r="31" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="122" t="s">
         <v>160</v>
       </c>
@@ -13448,10 +13452,10 @@
       <c r="D31" s="65"/>
       <c r="E31" s="52"/>
       <c r="F31" s="92"/>
-      <c r="G31" s="144"/>
+      <c r="G31" s="143"/>
       <c r="H31" s="73"/>
     </row>
-    <row r="32" spans="1:8" ht="24.75" customHeight="1">
+    <row r="32" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="125" t="s">
         <v>160</v>
       </c>
@@ -13460,10 +13464,10 @@
       <c r="D32" s="51"/>
       <c r="E32" s="52"/>
       <c r="F32" s="92"/>
-      <c r="G32" s="144"/>
+      <c r="G32" s="143"/>
       <c r="H32" s="73"/>
     </row>
-    <row r="33" spans="1:8" ht="24.75" customHeight="1">
+    <row r="33" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="125" t="s">
         <v>160</v>
       </c>
@@ -13472,10 +13476,10 @@
       <c r="D33" s="51"/>
       <c r="E33" s="52"/>
       <c r="F33" s="92"/>
-      <c r="G33" s="144"/>
+      <c r="G33" s="143"/>
       <c r="H33" s="73"/>
     </row>
-    <row r="34" spans="1:8" ht="24.75" customHeight="1">
+    <row r="34" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="121" t="s">
         <v>160</v>
       </c>
@@ -13484,10 +13488,10 @@
       <c r="D34" s="51"/>
       <c r="E34" s="52"/>
       <c r="F34" s="92"/>
-      <c r="G34" s="144"/>
+      <c r="G34" s="143"/>
       <c r="H34" s="73"/>
     </row>
-    <row r="35" spans="1:8" ht="24.75" customHeight="1">
+    <row r="35" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="125" t="s">
         <v>161</v>
       </c>
@@ -13496,10 +13500,10 @@
       <c r="D35" s="65"/>
       <c r="E35" s="52"/>
       <c r="F35" s="92"/>
-      <c r="G35" s="144"/>
+      <c r="G35" s="143"/>
       <c r="H35" s="73"/>
     </row>
-    <row r="36" spans="1:8" ht="24.75" customHeight="1">
+    <row r="36" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="125" t="s">
         <v>161</v>
       </c>
@@ -13508,10 +13512,10 @@
       <c r="D36" s="51"/>
       <c r="E36" s="52"/>
       <c r="F36" s="92"/>
-      <c r="G36" s="144"/>
+      <c r="G36" s="143"/>
       <c r="H36" s="73"/>
     </row>
-    <row r="37" spans="1:8" ht="24.75" customHeight="1">
+    <row r="37" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="125" t="s">
         <v>161</v>
       </c>
@@ -13520,34 +13524,34 @@
       <c r="D37" s="51"/>
       <c r="E37" s="52"/>
       <c r="F37" s="92"/>
-      <c r="G37" s="144"/>
+      <c r="G37" s="143"/>
       <c r="H37" s="73"/>
     </row>
-    <row r="38" spans="1:8" ht="24.75" customHeight="1">
+    <row r="38" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="125" t="s">
         <v>161</v>
       </c>
       <c r="B38" s="61"/>
       <c r="C38" s="61"/>
       <c r="D38" s="51"/>
-      <c r="E38" s="151"/>
+      <c r="E38" s="150"/>
       <c r="F38" s="92"/>
-      <c r="G38" s="145"/>
-      <c r="H38" s="152"/>
-    </row>
-    <row r="39" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A39" s="157" t="s">
+      <c r="G38" s="144"/>
+      <c r="H38" s="151"/>
+    </row>
+    <row r="39" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="156" t="s">
         <v>162</v>
       </c>
-      <c r="B39" s="157"/>
-      <c r="C39" s="157"/>
-      <c r="D39" s="157"/>
-      <c r="E39" s="157"/>
-      <c r="F39" s="157"/>
-      <c r="G39" s="157"/>
-      <c r="H39" s="157"/>
-    </row>
-    <row r="40" spans="1:8" ht="24.75" customHeight="1">
+      <c r="B39" s="156"/>
+      <c r="C39" s="156"/>
+      <c r="D39" s="156"/>
+      <c r="E39" s="156"/>
+      <c r="F39" s="156"/>
+      <c r="G39" s="156"/>
+      <c r="H39" s="156"/>
+    </row>
+    <row r="40" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="74" t="s">
         <v>163</v>
       </c>
@@ -13564,10 +13568,10 @@
       <c r="F40" s="69" t="s">
         <v>133</v>
       </c>
-      <c r="G40" s="146"/>
+      <c r="G40" s="145"/>
       <c r="H40" s="53"/>
     </row>
-    <row r="41" spans="1:8" ht="24.75" customHeight="1">
+    <row r="41" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="77" t="s">
         <v>163</v>
       </c>
@@ -13581,13 +13585,13 @@
       <c r="E41" s="56" t="s">
         <v>126</v>
       </c>
-      <c r="F41" s="137" t="s">
+      <c r="F41" s="136" t="s">
         <v>127</v>
       </c>
-      <c r="G41" s="144"/>
+      <c r="G41" s="143"/>
       <c r="H41" s="57"/>
     </row>
-    <row r="42" spans="1:8" ht="24.75" customHeight="1">
+    <row r="42" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="74" t="s">
         <v>163</v>
       </c>
@@ -13601,13 +13605,13 @@
       <c r="E42" s="56" t="s">
         <v>126</v>
       </c>
-      <c r="F42" s="137" t="s">
+      <c r="F42" s="136" t="s">
         <v>127</v>
       </c>
-      <c r="G42" s="144"/>
+      <c r="G42" s="143"/>
       <c r="H42" s="57"/>
     </row>
-    <row r="43" spans="1:8" ht="24.75" customHeight="1">
+    <row r="43" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="77" t="s">
         <v>163</v>
       </c>
@@ -13621,13 +13625,13 @@
       <c r="E43" s="56" t="s">
         <v>126</v>
       </c>
-      <c r="F43" s="137" t="s">
+      <c r="F43" s="136" t="s">
         <v>127</v>
       </c>
-      <c r="G43" s="144"/>
+      <c r="G43" s="143"/>
       <c r="H43" s="57"/>
     </row>
-    <row r="44" spans="1:8" ht="24.75" customHeight="1">
+    <row r="44" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="74" t="s">
         <v>163</v>
       </c>
@@ -13641,13 +13645,15 @@
       <c r="E44" s="56" t="s">
         <v>126</v>
       </c>
-      <c r="F44" s="137" t="s">
+      <c r="F44" s="136" t="s">
         <v>127</v>
       </c>
-      <c r="G44" s="144"/>
+      <c r="G44" s="143" t="s">
+        <v>126</v>
+      </c>
       <c r="H44" s="57"/>
     </row>
-    <row r="45" spans="1:8" ht="24.75" customHeight="1">
+    <row r="45" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="80" t="s">
         <v>163</v>
       </c>
@@ -13661,13 +13667,13 @@
       <c r="E45" s="56" t="s">
         <v>126</v>
       </c>
-      <c r="F45" s="137" t="s">
+      <c r="F45" s="136" t="s">
         <v>127</v>
       </c>
-      <c r="G45" s="144"/>
+      <c r="G45" s="143"/>
       <c r="H45" s="57"/>
     </row>
-    <row r="46" spans="1:8" ht="24.75" customHeight="1">
+    <row r="46" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="83" t="s">
         <v>170</v>
       </c>
@@ -13681,13 +13687,13 @@
       <c r="E46" s="56" t="s">
         <v>126</v>
       </c>
-      <c r="F46" s="137" t="s">
+      <c r="F46" s="136" t="s">
         <v>127</v>
       </c>
-      <c r="G46" s="144"/>
+      <c r="G46" s="143"/>
       <c r="H46" s="57"/>
     </row>
-    <row r="47" spans="1:8" ht="24.75" customHeight="1">
+    <row r="47" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="77" t="s">
         <v>170</v>
       </c>
@@ -13700,10 +13706,10 @@
       </c>
       <c r="E47" s="56"/>
       <c r="F47" s="128"/>
-      <c r="G47" s="144"/>
+      <c r="G47" s="143"/>
       <c r="H47" s="57"/>
     </row>
-    <row r="48" spans="1:8" ht="24.75" customHeight="1">
+    <row r="48" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="74" t="s">
         <v>170</v>
       </c>
@@ -13720,10 +13726,10 @@
       <c r="F48" s="128" t="s">
         <v>133</v>
       </c>
-      <c r="G48" s="144"/>
+      <c r="G48" s="143"/>
       <c r="H48" s="57"/>
     </row>
-    <row r="49" spans="1:8" ht="24.75" customHeight="1">
+    <row r="49" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="77" t="s">
         <v>170</v>
       </c>
@@ -13736,10 +13742,10 @@
       </c>
       <c r="E49" s="56"/>
       <c r="F49" s="128"/>
-      <c r="G49" s="144"/>
+      <c r="G49" s="143"/>
       <c r="H49" s="57"/>
     </row>
-    <row r="50" spans="1:8" ht="24.75" customHeight="1">
+    <row r="50" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="74" t="s">
         <v>170</v>
       </c>
@@ -13753,13 +13759,13 @@
       <c r="E50" s="56" t="s">
         <v>126</v>
       </c>
-      <c r="F50" s="137" t="s">
+      <c r="F50" s="136" t="s">
         <v>127</v>
       </c>
-      <c r="G50" s="144"/>
+      <c r="G50" s="143"/>
       <c r="H50" s="57"/>
     </row>
-    <row r="51" spans="1:8" ht="24.75" customHeight="1">
+    <row r="51" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="77" t="s">
         <v>170</v>
       </c>
@@ -13772,10 +13778,10 @@
       </c>
       <c r="E51" s="56"/>
       <c r="F51" s="128"/>
-      <c r="G51" s="144"/>
+      <c r="G51" s="143"/>
       <c r="H51" s="57"/>
     </row>
-    <row r="52" spans="1:8" ht="24.75" customHeight="1">
+    <row r="52" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="86" t="s">
         <v>170</v>
       </c>
@@ -13789,13 +13795,13 @@
       <c r="E52" s="56" t="s">
         <v>126</v>
       </c>
-      <c r="F52" s="137" t="s">
+      <c r="F52" s="136" t="s">
         <v>127</v>
       </c>
-      <c r="G52" s="144"/>
+      <c r="G52" s="143"/>
       <c r="H52" s="57"/>
     </row>
-    <row r="53" spans="1:8" ht="24.75" customHeight="1">
+    <row r="53" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="88" t="s">
         <v>178</v>
       </c>
@@ -13812,10 +13818,10 @@
       <c r="F53" s="128" t="s">
         <v>127</v>
       </c>
-      <c r="G53" s="144"/>
+      <c r="G53" s="143"/>
       <c r="H53" s="57"/>
     </row>
-    <row r="54" spans="1:8" ht="24.75" customHeight="1">
+    <row r="54" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="74" t="s">
         <v>178</v>
       </c>
@@ -13832,10 +13838,10 @@
       <c r="F54" s="128" t="s">
         <v>127</v>
       </c>
-      <c r="G54" s="144"/>
+      <c r="G54" s="143"/>
       <c r="H54" s="57"/>
     </row>
-    <row r="55" spans="1:8" ht="24.75" customHeight="1">
+    <row r="55" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="77" t="s">
         <v>178</v>
       </c>
@@ -13852,10 +13858,10 @@
       <c r="F55" s="128" t="s">
         <v>127</v>
       </c>
-      <c r="G55" s="144"/>
+      <c r="G55" s="143"/>
       <c r="H55" s="57"/>
     </row>
-    <row r="56" spans="1:8" ht="24.75" customHeight="1">
+    <row r="56" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="74" t="s">
         <v>178</v>
       </c>
@@ -13872,10 +13878,10 @@
       <c r="F56" s="128" t="s">
         <v>127</v>
       </c>
-      <c r="G56" s="144"/>
+      <c r="G56" s="143"/>
       <c r="H56" s="57"/>
     </row>
-    <row r="57" spans="1:8" ht="24.75" customHeight="1">
+    <row r="57" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="80" t="s">
         <v>178</v>
       </c>
@@ -13892,10 +13898,10 @@
       <c r="F57" s="128" t="s">
         <v>127</v>
       </c>
-      <c r="G57" s="144"/>
+      <c r="G57" s="143"/>
       <c r="H57" s="57"/>
     </row>
-    <row r="58" spans="1:8" ht="24.75" customHeight="1">
+    <row r="58" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="83" t="s">
         <v>184</v>
       </c>
@@ -13909,13 +13915,13 @@
       <c r="E58" s="56" t="s">
         <v>126</v>
       </c>
-      <c r="F58" s="137" t="s">
+      <c r="F58" s="136" t="s">
         <v>127</v>
       </c>
-      <c r="G58" s="144"/>
+      <c r="G58" s="143"/>
       <c r="H58" s="57"/>
     </row>
-    <row r="59" spans="1:8" ht="24.75" customHeight="1">
+    <row r="59" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="77" t="s">
         <v>184</v>
       </c>
@@ -13929,13 +13935,13 @@
       <c r="E59" s="56" t="s">
         <v>126</v>
       </c>
-      <c r="F59" s="137" t="s">
+      <c r="F59" s="136" t="s">
         <v>127</v>
       </c>
-      <c r="G59" s="144"/>
+      <c r="G59" s="143"/>
       <c r="H59" s="57"/>
     </row>
-    <row r="60" spans="1:8" ht="24.75" customHeight="1">
+    <row r="60" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="74" t="s">
         <v>184</v>
       </c>
@@ -13949,13 +13955,13 @@
       <c r="E60" s="56" t="s">
         <v>126</v>
       </c>
-      <c r="F60" s="137" t="s">
+      <c r="F60" s="136" t="s">
         <v>127</v>
       </c>
-      <c r="G60" s="144"/>
+      <c r="G60" s="143"/>
       <c r="H60" s="57"/>
     </row>
-    <row r="61" spans="1:8" ht="24.75" customHeight="1">
+    <row r="61" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="80" t="s">
         <v>184</v>
       </c>
@@ -13969,13 +13975,13 @@
       <c r="E61" s="56" t="s">
         <v>126</v>
       </c>
-      <c r="F61" s="137" t="s">
+      <c r="F61" s="136" t="s">
         <v>127</v>
       </c>
-      <c r="G61" s="144"/>
+      <c r="G61" s="143"/>
       <c r="H61" s="57"/>
     </row>
-    <row r="62" spans="1:8" ht="24.75" customHeight="1">
+    <row r="62" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="83" t="s">
         <v>189</v>
       </c>
@@ -13992,10 +13998,10 @@
       <c r="F62" s="128" t="s">
         <v>127</v>
       </c>
-      <c r="G62" s="144"/>
+      <c r="G62" s="143"/>
       <c r="H62" s="57"/>
     </row>
-    <row r="63" spans="1:8" ht="24.75" customHeight="1">
+    <row r="63" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="77" t="s">
         <v>189</v>
       </c>
@@ -14012,10 +14018,10 @@
       <c r="F63" s="128" t="s">
         <v>127</v>
       </c>
-      <c r="G63" s="144"/>
+      <c r="G63" s="143"/>
       <c r="H63" s="57"/>
     </row>
-    <row r="64" spans="1:8" ht="24.75" customHeight="1">
+    <row r="64" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="86" t="s">
         <v>189</v>
       </c>
@@ -14032,10 +14038,10 @@
       <c r="F64" s="128" t="s">
         <v>127</v>
       </c>
-      <c r="G64" s="144"/>
+      <c r="G64" s="143"/>
       <c r="H64" s="57"/>
     </row>
-    <row r="65" spans="1:8" ht="24.75" customHeight="1">
+    <row r="65" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="88" t="s">
         <v>193</v>
       </c>
@@ -14052,10 +14058,10 @@
       <c r="F65" s="128" t="s">
         <v>127</v>
       </c>
-      <c r="G65" s="144"/>
+      <c r="G65" s="143"/>
       <c r="H65" s="57"/>
     </row>
-    <row r="66" spans="1:8" ht="24.75" customHeight="1">
+    <row r="66" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="74" t="s">
         <v>193</v>
       </c>
@@ -14072,10 +14078,10 @@
       <c r="F66" s="128" t="s">
         <v>127</v>
       </c>
-      <c r="G66" s="144"/>
+      <c r="G66" s="143"/>
       <c r="H66" s="57"/>
     </row>
-    <row r="67" spans="1:8" ht="24.75" customHeight="1">
+    <row r="67" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="77" t="s">
         <v>193</v>
       </c>
@@ -14088,10 +14094,10 @@
       </c>
       <c r="E67" s="56"/>
       <c r="F67" s="128"/>
-      <c r="G67" s="144"/>
+      <c r="G67" s="143"/>
       <c r="H67" s="57"/>
     </row>
-    <row r="68" spans="1:8" ht="24.75" customHeight="1">
+    <row r="68" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="86" t="s">
         <v>193</v>
       </c>
@@ -14104,10 +14110,10 @@
       </c>
       <c r="E68" s="56"/>
       <c r="F68" s="128"/>
-      <c r="G68" s="144"/>
+      <c r="G68" s="143"/>
       <c r="H68" s="57"/>
     </row>
-    <row r="69" spans="1:8" ht="24.75" customHeight="1">
+    <row r="69" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="122" t="s">
         <v>198</v>
       </c>
@@ -14116,10 +14122,10 @@
       <c r="D69" s="65"/>
       <c r="E69" s="127"/>
       <c r="F69" s="128"/>
-      <c r="G69" s="144"/>
+      <c r="G69" s="143"/>
       <c r="H69" s="57"/>
     </row>
-    <row r="70" spans="1:8" ht="24.75" customHeight="1">
+    <row r="70" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="125" t="s">
         <v>198</v>
       </c>
@@ -14128,10 +14134,10 @@
       <c r="D70" s="51"/>
       <c r="E70" s="127"/>
       <c r="F70" s="128"/>
-      <c r="G70" s="144"/>
+      <c r="G70" s="143"/>
       <c r="H70" s="57"/>
     </row>
-    <row r="71" spans="1:8" ht="24.75" customHeight="1">
+    <row r="71" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="125" t="s">
         <v>198</v>
       </c>
@@ -14140,10 +14146,10 @@
       <c r="D71" s="51"/>
       <c r="E71" s="127"/>
       <c r="F71" s="128"/>
-      <c r="G71" s="144"/>
+      <c r="G71" s="143"/>
       <c r="H71" s="57"/>
     </row>
-    <row r="72" spans="1:8" ht="24.75" customHeight="1">
+    <row r="72" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="125" t="s">
         <v>198</v>
       </c>
@@ -14152,10 +14158,10 @@
       <c r="D72" s="51"/>
       <c r="E72" s="127"/>
       <c r="F72" s="128"/>
-      <c r="G72" s="144"/>
+      <c r="G72" s="143"/>
       <c r="H72" s="57"/>
     </row>
-    <row r="73" spans="1:8" ht="24.75" customHeight="1">
+    <row r="73" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="125" t="s">
         <v>198</v>
       </c>
@@ -14164,10 +14170,10 @@
       <c r="D73" s="51"/>
       <c r="E73" s="127"/>
       <c r="F73" s="128"/>
-      <c r="G73" s="144"/>
+      <c r="G73" s="143"/>
       <c r="H73" s="57"/>
     </row>
-    <row r="74" spans="1:8" ht="24.75" customHeight="1">
+    <row r="74" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="122" t="s">
         <v>199</v>
       </c>
@@ -14176,10 +14182,10 @@
       <c r="D74" s="65"/>
       <c r="E74" s="127"/>
       <c r="F74" s="128"/>
-      <c r="G74" s="144"/>
+      <c r="G74" s="143"/>
       <c r="H74" s="57"/>
     </row>
-    <row r="75" spans="1:8" ht="24.75" customHeight="1">
+    <row r="75" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="125" t="s">
         <v>199</v>
       </c>
@@ -14188,10 +14194,10 @@
       <c r="D75" s="51"/>
       <c r="E75" s="127"/>
       <c r="F75" s="128"/>
-      <c r="G75" s="144"/>
+      <c r="G75" s="143"/>
       <c r="H75" s="57"/>
     </row>
-    <row r="76" spans="1:8" ht="24.75" customHeight="1">
+    <row r="76" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="125" t="s">
         <v>199</v>
       </c>
@@ -14200,10 +14206,10 @@
       <c r="D76" s="51"/>
       <c r="E76" s="127"/>
       <c r="F76" s="128"/>
-      <c r="G76" s="144"/>
+      <c r="G76" s="143"/>
       <c r="H76" s="57"/>
     </row>
-    <row r="77" spans="1:8" ht="24.75" customHeight="1">
+    <row r="77" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="125" t="s">
         <v>199</v>
       </c>
@@ -14212,10 +14218,10 @@
       <c r="D77" s="51"/>
       <c r="E77" s="127"/>
       <c r="F77" s="128"/>
-      <c r="G77" s="144"/>
+      <c r="G77" s="143"/>
       <c r="H77" s="57"/>
     </row>
-    <row r="78" spans="1:8" ht="24.75" customHeight="1">
+    <row r="78" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="122" t="s">
         <v>200</v>
       </c>
@@ -14224,10 +14230,10 @@
       <c r="D78" s="65"/>
       <c r="E78" s="127"/>
       <c r="F78" s="128"/>
-      <c r="G78" s="144"/>
+      <c r="G78" s="143"/>
       <c r="H78" s="57"/>
     </row>
-    <row r="79" spans="1:8" ht="24.75" customHeight="1">
+    <row r="79" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="125" t="s">
         <v>200</v>
       </c>
@@ -14236,10 +14242,10 @@
       <c r="D79" s="51"/>
       <c r="E79" s="127"/>
       <c r="F79" s="128"/>
-      <c r="G79" s="144"/>
+      <c r="G79" s="143"/>
       <c r="H79" s="57"/>
     </row>
-    <row r="80" spans="1:8" ht="24.75" customHeight="1">
+    <row r="80" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="125" t="s">
         <v>200</v>
       </c>
@@ -14248,10 +14254,10 @@
       <c r="D80" s="51"/>
       <c r="E80" s="127"/>
       <c r="F80" s="128"/>
-      <c r="G80" s="144"/>
+      <c r="G80" s="143"/>
       <c r="H80" s="57"/>
     </row>
-    <row r="81" spans="1:8" ht="24.75" customHeight="1">
+    <row r="81" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="125" t="s">
         <v>200</v>
       </c>
@@ -14260,34 +14266,34 @@
       <c r="D81" s="51"/>
       <c r="E81" s="127"/>
       <c r="F81" s="128"/>
-      <c r="G81" s="144"/>
+      <c r="G81" s="143"/>
       <c r="H81" s="57"/>
     </row>
-    <row r="82" spans="1:8" ht="24.75" customHeight="1">
+    <row r="82" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="125" t="s">
         <v>200</v>
       </c>
       <c r="B82" s="61"/>
       <c r="C82" s="61"/>
       <c r="D82" s="51"/>
-      <c r="E82" s="153"/>
+      <c r="E82" s="152"/>
       <c r="F82" s="92"/>
-      <c r="G82" s="145"/>
+      <c r="G82" s="144"/>
       <c r="H82" s="73"/>
     </row>
-    <row r="83" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A83" s="158" t="s">
+    <row r="83" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="157" t="s">
         <v>201</v>
       </c>
-      <c r="B83" s="158"/>
-      <c r="C83" s="158"/>
-      <c r="D83" s="158"/>
-      <c r="E83" s="158"/>
-      <c r="F83" s="158"/>
-      <c r="G83" s="158"/>
-      <c r="H83" s="158"/>
-    </row>
-    <row r="84" spans="1:8" ht="24.75" customHeight="1">
+      <c r="B83" s="157"/>
+      <c r="C83" s="157"/>
+      <c r="D83" s="157"/>
+      <c r="E83" s="157"/>
+      <c r="F83" s="157"/>
+      <c r="G83" s="157"/>
+      <c r="H83" s="157"/>
+    </row>
+    <row r="84" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="77" t="s">
         <v>202</v>
       </c>
@@ -14300,10 +14306,10 @@
       </c>
       <c r="E84" s="52"/>
       <c r="F84" s="69"/>
-      <c r="G84" s="146"/>
+      <c r="G84" s="145"/>
       <c r="H84" s="53"/>
     </row>
-    <row r="85" spans="1:8" ht="24.75" customHeight="1">
+    <row r="85" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="74" t="s">
         <v>202</v>
       </c>
@@ -14320,10 +14326,10 @@
       <c r="F85" s="128" t="s">
         <v>127</v>
       </c>
-      <c r="G85" s="144"/>
+      <c r="G85" s="143"/>
       <c r="H85" s="57"/>
     </row>
-    <row r="86" spans="1:8" ht="24.75" customHeight="1">
+    <row r="86" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="77" t="s">
         <v>202</v>
       </c>
@@ -14340,10 +14346,10 @@
       <c r="F86" s="128" t="s">
         <v>127</v>
       </c>
-      <c r="G86" s="144"/>
+      <c r="G86" s="143"/>
       <c r="H86" s="57"/>
     </row>
-    <row r="87" spans="1:8" ht="24.75" customHeight="1">
+    <row r="87" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="74" t="s">
         <v>202</v>
       </c>
@@ -14356,10 +14362,10 @@
       </c>
       <c r="E87" s="56"/>
       <c r="F87" s="128"/>
-      <c r="G87" s="144"/>
+      <c r="G87" s="143"/>
       <c r="H87" s="57"/>
     </row>
-    <row r="88" spans="1:8" ht="24.75" customHeight="1">
+    <row r="88" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="80" t="s">
         <v>202</v>
       </c>
@@ -14376,10 +14382,10 @@
       <c r="F88" s="92" t="s">
         <v>127</v>
       </c>
-      <c r="G88" s="144"/>
+      <c r="G88" s="143"/>
       <c r="H88" s="73"/>
     </row>
-    <row r="89" spans="1:8" ht="24.75" customHeight="1">
+    <row r="89" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="83" t="s">
         <v>202</v>
       </c>
@@ -14396,10 +14402,10 @@
       <c r="F89" s="128" t="s">
         <v>127</v>
       </c>
-      <c r="G89" s="144"/>
+      <c r="G89" s="143"/>
       <c r="H89" s="57"/>
     </row>
-    <row r="90" spans="1:8" ht="24.75" customHeight="1">
+    <row r="90" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="80" t="s">
         <v>202</v>
       </c>
@@ -14416,10 +14422,10 @@
       <c r="F90" s="92" t="s">
         <v>127</v>
       </c>
-      <c r="G90" s="144"/>
+      <c r="G90" s="143"/>
       <c r="H90" s="73"/>
     </row>
-    <row r="91" spans="1:8" ht="24.75" customHeight="1">
+    <row r="91" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="122" t="s">
         <v>210</v>
       </c>
@@ -14428,10 +14434,10 @@
       <c r="D91" s="120"/>
       <c r="E91" s="91"/>
       <c r="F91" s="92"/>
-      <c r="G91" s="144"/>
+      <c r="G91" s="143"/>
       <c r="H91" s="73"/>
     </row>
-    <row r="92" spans="1:8" ht="24.75" customHeight="1">
+    <row r="92" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="125" t="s">
         <v>210</v>
       </c>
@@ -14440,10 +14446,10 @@
       <c r="D92" s="119"/>
       <c r="E92" s="91"/>
       <c r="F92" s="92"/>
-      <c r="G92" s="144"/>
+      <c r="G92" s="143"/>
       <c r="H92" s="73"/>
     </row>
-    <row r="93" spans="1:8" ht="24.75" customHeight="1">
+    <row r="93" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="125" t="s">
         <v>210</v>
       </c>
@@ -14452,10 +14458,10 @@
       <c r="D93" s="119"/>
       <c r="E93" s="91"/>
       <c r="F93" s="92"/>
-      <c r="G93" s="144"/>
+      <c r="G93" s="143"/>
       <c r="H93" s="73"/>
     </row>
-    <row r="94" spans="1:8" ht="24.75" customHeight="1">
+    <row r="94" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="125" t="s">
         <v>210</v>
       </c>
@@ -14464,22 +14470,22 @@
       <c r="D94" s="119"/>
       <c r="E94" s="91"/>
       <c r="F94" s="92"/>
-      <c r="G94" s="145"/>
+      <c r="G94" s="144"/>
       <c r="H94" s="73"/>
     </row>
-    <row r="95" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A95" s="158" t="s">
+    <row r="95" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="157" t="s">
         <v>211</v>
       </c>
-      <c r="B95" s="158"/>
-      <c r="C95" s="158"/>
-      <c r="D95" s="158"/>
-      <c r="E95" s="158"/>
-      <c r="F95" s="158"/>
-      <c r="G95" s="158"/>
-      <c r="H95" s="158"/>
-    </row>
-    <row r="96" spans="1:8" ht="24.75" customHeight="1">
+      <c r="B95" s="157"/>
+      <c r="C95" s="157"/>
+      <c r="D95" s="157"/>
+      <c r="E95" s="157"/>
+      <c r="F95" s="157"/>
+      <c r="G95" s="157"/>
+      <c r="H95" s="157"/>
+    </row>
+    <row r="96" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="74" t="s">
         <v>212</v>
       </c>
@@ -14491,11 +14497,11 @@
         <v>46275</v>
       </c>
       <c r="E96" s="110"/>
-      <c r="F96" s="138"/>
-      <c r="G96" s="146"/>
+      <c r="F96" s="137"/>
+      <c r="G96" s="145"/>
       <c r="H96" s="103"/>
     </row>
-    <row r="97" spans="1:8" ht="24.75" customHeight="1">
+    <row r="97" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="77" t="s">
         <v>212</v>
       </c>
@@ -14507,11 +14513,11 @@
         <v>46275</v>
       </c>
       <c r="E97" s="100"/>
-      <c r="F97" s="139"/>
-      <c r="G97" s="144"/>
+      <c r="F97" s="138"/>
+      <c r="G97" s="143"/>
       <c r="H97" s="101"/>
     </row>
-    <row r="98" spans="1:8" ht="24.75" customHeight="1">
+    <row r="98" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="74" t="s">
         <v>212</v>
       </c>
@@ -14523,11 +14529,11 @@
         <v>46275</v>
       </c>
       <c r="E98" s="100"/>
-      <c r="F98" s="139"/>
-      <c r="G98" s="144"/>
+      <c r="F98" s="138"/>
+      <c r="G98" s="143"/>
       <c r="H98" s="101"/>
     </row>
-    <row r="99" spans="1:8" ht="24.75" customHeight="1">
+    <row r="99" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="77" t="s">
         <v>212</v>
       </c>
@@ -14539,11 +14545,11 @@
         <v>46275</v>
       </c>
       <c r="E99" s="100"/>
-      <c r="F99" s="139"/>
-      <c r="G99" s="144"/>
+      <c r="F99" s="138"/>
+      <c r="G99" s="143"/>
       <c r="H99" s="101"/>
     </row>
-    <row r="100" spans="1:8" ht="24.75" customHeight="1">
+    <row r="100" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="74" t="s">
         <v>212</v>
       </c>
@@ -14555,11 +14561,11 @@
         <v>46275</v>
       </c>
       <c r="E100" s="100"/>
-      <c r="F100" s="139"/>
-      <c r="G100" s="144"/>
+      <c r="F100" s="138"/>
+      <c r="G100" s="143"/>
       <c r="H100" s="101"/>
     </row>
-    <row r="101" spans="1:8" ht="24.75" customHeight="1">
+    <row r="101" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="77" t="s">
         <v>212</v>
       </c>
@@ -14571,11 +14577,11 @@
         <v>46275</v>
       </c>
       <c r="E101" s="100"/>
-      <c r="F101" s="139"/>
-      <c r="G101" s="144"/>
+      <c r="F101" s="138"/>
+      <c r="G101" s="143"/>
       <c r="H101" s="101"/>
     </row>
-    <row r="102" spans="1:8" ht="24.75" customHeight="1">
+    <row r="102" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="86" t="s">
         <v>212</v>
       </c>
@@ -14587,11 +14593,11 @@
         <v>46275</v>
       </c>
       <c r="E102" s="100"/>
-      <c r="F102" s="139"/>
-      <c r="G102" s="144"/>
+      <c r="F102" s="138"/>
+      <c r="G102" s="143"/>
       <c r="H102" s="101"/>
     </row>
-    <row r="103" spans="1:8" ht="24.75" customHeight="1">
+    <row r="103" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="88" t="s">
         <v>220</v>
       </c>
@@ -14603,11 +14609,11 @@
         <v>46275</v>
       </c>
       <c r="E103" s="100"/>
-      <c r="F103" s="139"/>
-      <c r="G103" s="144"/>
+      <c r="F103" s="138"/>
+      <c r="G103" s="143"/>
       <c r="H103" s="101"/>
     </row>
-    <row r="104" spans="1:8" ht="24.75" customHeight="1">
+    <row r="104" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="74" t="s">
         <v>220</v>
       </c>
@@ -14619,11 +14625,11 @@
         <v>46275</v>
       </c>
       <c r="E104" s="100"/>
-      <c r="F104" s="139"/>
-      <c r="G104" s="144"/>
+      <c r="F104" s="138"/>
+      <c r="G104" s="143"/>
       <c r="H104" s="101"/>
     </row>
-    <row r="105" spans="1:8" ht="24.75" customHeight="1">
+    <row r="105" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="77" t="s">
         <v>220</v>
       </c>
@@ -14635,11 +14641,11 @@
         <v>46275</v>
       </c>
       <c r="E105" s="100"/>
-      <c r="F105" s="139"/>
-      <c r="G105" s="144"/>
+      <c r="F105" s="138"/>
+      <c r="G105" s="143"/>
       <c r="H105" s="101"/>
     </row>
-    <row r="106" spans="1:8" ht="24.75" customHeight="1">
+    <row r="106" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="74" t="s">
         <v>220</v>
       </c>
@@ -14651,11 +14657,11 @@
         <v>46275</v>
       </c>
       <c r="E106" s="100"/>
-      <c r="F106" s="139"/>
-      <c r="G106" s="144"/>
+      <c r="F106" s="138"/>
+      <c r="G106" s="143"/>
       <c r="H106" s="101"/>
     </row>
-    <row r="107" spans="1:8" ht="24.75" customHeight="1">
+    <row r="107" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="77" t="s">
         <v>220</v>
       </c>
@@ -14667,11 +14673,11 @@
         <v>46275</v>
       </c>
       <c r="E107" s="100"/>
-      <c r="F107" s="139"/>
-      <c r="G107" s="144"/>
+      <c r="F107" s="138"/>
+      <c r="G107" s="143"/>
       <c r="H107" s="101"/>
     </row>
-    <row r="108" spans="1:8" ht="24.75" customHeight="1">
+    <row r="108" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="74" t="s">
         <v>220</v>
       </c>
@@ -14683,11 +14689,11 @@
         <v>46275</v>
       </c>
       <c r="E108" s="100"/>
-      <c r="F108" s="139"/>
-      <c r="G108" s="144"/>
+      <c r="F108" s="138"/>
+      <c r="G108" s="143"/>
       <c r="H108" s="101"/>
     </row>
-    <row r="109" spans="1:8" ht="24.75" customHeight="1">
+    <row r="109" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="98" t="s">
         <v>220</v>
       </c>
@@ -14699,11 +14705,11 @@
         <v>46275</v>
       </c>
       <c r="E109" s="100"/>
-      <c r="F109" s="139"/>
-      <c r="G109" s="144"/>
+      <c r="F109" s="138"/>
+      <c r="G109" s="143"/>
       <c r="H109" s="101"/>
     </row>
-    <row r="110" spans="1:8" ht="24.75" customHeight="1">
+    <row r="110" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="74" t="s">
         <v>228</v>
       </c>
@@ -14714,11 +14720,11 @@
         <v>46275</v>
       </c>
       <c r="E110" s="100"/>
-      <c r="F110" s="139"/>
-      <c r="G110" s="144"/>
+      <c r="F110" s="138"/>
+      <c r="G110" s="143"/>
       <c r="H110" s="101"/>
     </row>
-    <row r="111" spans="1:8" ht="24.75" customHeight="1">
+    <row r="111" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="77" t="s">
         <v>228</v>
       </c>
@@ -14730,11 +14736,11 @@
         <v>46275</v>
       </c>
       <c r="E111" s="100"/>
-      <c r="F111" s="139"/>
-      <c r="G111" s="144"/>
+      <c r="F111" s="138"/>
+      <c r="G111" s="143"/>
       <c r="H111" s="101"/>
     </row>
-    <row r="112" spans="1:8" ht="24.75" customHeight="1">
+    <row r="112" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="74" t="s">
         <v>228</v>
       </c>
@@ -14746,11 +14752,11 @@
         <v>46275</v>
       </c>
       <c r="E112" s="100"/>
-      <c r="F112" s="139"/>
-      <c r="G112" s="144"/>
+      <c r="F112" s="138"/>
+      <c r="G112" s="143"/>
       <c r="H112" s="101"/>
     </row>
-    <row r="113" spans="1:8" ht="24.75" customHeight="1">
+    <row r="113" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="77" t="s">
         <v>228</v>
       </c>
@@ -14762,11 +14768,11 @@
         <v>46275</v>
       </c>
       <c r="E113" s="100"/>
-      <c r="F113" s="139"/>
-      <c r="G113" s="144"/>
+      <c r="F113" s="138"/>
+      <c r="G113" s="143"/>
       <c r="H113" s="101"/>
     </row>
-    <row r="114" spans="1:8" ht="24.75" customHeight="1">
+    <row r="114" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="74" t="s">
         <v>228</v>
       </c>
@@ -14778,11 +14784,11 @@
         <v>46275</v>
       </c>
       <c r="E114" s="100"/>
-      <c r="F114" s="139"/>
-      <c r="G114" s="144"/>
+      <c r="F114" s="138"/>
+      <c r="G114" s="143"/>
       <c r="H114" s="101"/>
     </row>
-    <row r="115" spans="1:8" ht="24.75" customHeight="1">
+    <row r="115" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="77" t="s">
         <v>228</v>
       </c>
@@ -14794,11 +14800,11 @@
         <v>46275</v>
       </c>
       <c r="E115" s="100"/>
-      <c r="F115" s="139"/>
-      <c r="G115" s="144"/>
+      <c r="F115" s="138"/>
+      <c r="G115" s="143"/>
       <c r="H115" s="101"/>
     </row>
-    <row r="116" spans="1:8" ht="24.75" customHeight="1">
+    <row r="116" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="86" t="s">
         <v>228</v>
       </c>
@@ -14810,11 +14816,11 @@
         <v>46275</v>
       </c>
       <c r="E116" s="100"/>
-      <c r="F116" s="139"/>
-      <c r="G116" s="144"/>
+      <c r="F116" s="138"/>
+      <c r="G116" s="143"/>
       <c r="H116" s="101"/>
     </row>
-    <row r="117" spans="1:8" ht="24.75" customHeight="1">
+    <row r="117" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="88" t="s">
         <v>236</v>
       </c>
@@ -14826,11 +14832,11 @@
         <v>46275</v>
       </c>
       <c r="E117" s="100"/>
-      <c r="F117" s="139"/>
-      <c r="G117" s="144"/>
+      <c r="F117" s="138"/>
+      <c r="G117" s="143"/>
       <c r="H117" s="101"/>
     </row>
-    <row r="118" spans="1:8" ht="24.75" customHeight="1">
+    <row r="118" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="74" t="s">
         <v>236</v>
       </c>
@@ -14842,11 +14848,11 @@
         <v>46275</v>
       </c>
       <c r="E118" s="100"/>
-      <c r="F118" s="139"/>
-      <c r="G118" s="144"/>
+      <c r="F118" s="138"/>
+      <c r="G118" s="143"/>
       <c r="H118" s="101"/>
     </row>
-    <row r="119" spans="1:8" ht="24.75" customHeight="1">
+    <row r="119" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="77" t="s">
         <v>236</v>
       </c>
@@ -14858,11 +14864,11 @@
         <v>46275</v>
       </c>
       <c r="E119" s="100"/>
-      <c r="F119" s="139"/>
-      <c r="G119" s="144"/>
+      <c r="F119" s="138"/>
+      <c r="G119" s="143"/>
       <c r="H119" s="101"/>
     </row>
-    <row r="120" spans="1:8" ht="24.75" customHeight="1">
+    <row r="120" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="74" t="s">
         <v>236</v>
       </c>
@@ -14874,11 +14880,11 @@
         <v>46275</v>
       </c>
       <c r="E120" s="100"/>
-      <c r="F120" s="139"/>
-      <c r="G120" s="144"/>
+      <c r="F120" s="138"/>
+      <c r="G120" s="143"/>
       <c r="H120" s="101"/>
     </row>
-    <row r="121" spans="1:8" ht="24.75" customHeight="1">
+    <row r="121" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="77" t="s">
         <v>236</v>
       </c>
@@ -14890,11 +14896,11 @@
         <v>46275</v>
       </c>
       <c r="E121" s="100"/>
-      <c r="F121" s="139"/>
-      <c r="G121" s="144"/>
+      <c r="F121" s="138"/>
+      <c r="G121" s="143"/>
       <c r="H121" s="101"/>
     </row>
-    <row r="122" spans="1:8" ht="24.75" customHeight="1">
+    <row r="122" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="74" t="s">
         <v>236</v>
       </c>
@@ -14906,11 +14912,11 @@
         <v>46305</v>
       </c>
       <c r="E122" s="100"/>
-      <c r="F122" s="139"/>
-      <c r="G122" s="144"/>
+      <c r="F122" s="138"/>
+      <c r="G122" s="143"/>
       <c r="H122" s="101"/>
     </row>
-    <row r="123" spans="1:8" ht="24.75" customHeight="1">
+    <row r="123" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="80" t="s">
         <v>236</v>
       </c>
@@ -14922,11 +14928,11 @@
         <v>46275</v>
       </c>
       <c r="E123" s="100"/>
-      <c r="F123" s="139"/>
-      <c r="G123" s="144"/>
+      <c r="F123" s="138"/>
+      <c r="G123" s="143"/>
       <c r="H123" s="101"/>
     </row>
-    <row r="124" spans="1:8" ht="24.75" customHeight="1">
+    <row r="124" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="83" t="s">
         <v>243</v>
       </c>
@@ -14938,11 +14944,11 @@
         <v>46305</v>
       </c>
       <c r="E124" s="100"/>
-      <c r="F124" s="139"/>
-      <c r="G124" s="144"/>
+      <c r="F124" s="138"/>
+      <c r="G124" s="143"/>
       <c r="H124" s="101"/>
     </row>
-    <row r="125" spans="1:8" ht="24.75" customHeight="1">
+    <row r="125" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="77" t="s">
         <v>243</v>
       </c>
@@ -14954,11 +14960,11 @@
         <v>46305</v>
       </c>
       <c r="E125" s="100"/>
-      <c r="F125" s="139"/>
-      <c r="G125" s="144"/>
+      <c r="F125" s="138"/>
+      <c r="G125" s="143"/>
       <c r="H125" s="101"/>
     </row>
-    <row r="126" spans="1:8" ht="24.75" customHeight="1">
+    <row r="126" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="74" t="s">
         <v>243</v>
       </c>
@@ -14970,11 +14976,11 @@
         <v>46305</v>
       </c>
       <c r="E126" s="100"/>
-      <c r="F126" s="139"/>
-      <c r="G126" s="144"/>
+      <c r="F126" s="138"/>
+      <c r="G126" s="143"/>
       <c r="H126" s="101"/>
     </row>
-    <row r="127" spans="1:8" ht="24.75" customHeight="1">
+    <row r="127" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="77" t="s">
         <v>243</v>
       </c>
@@ -14986,11 +14992,11 @@
         <v>46305</v>
       </c>
       <c r="E127" s="100"/>
-      <c r="F127" s="139"/>
-      <c r="G127" s="144"/>
+      <c r="F127" s="138"/>
+      <c r="G127" s="143"/>
       <c r="H127" s="101"/>
     </row>
-    <row r="128" spans="1:8" ht="24.75" customHeight="1">
+    <row r="128" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="74" t="s">
         <v>243</v>
       </c>
@@ -15002,11 +15008,11 @@
         <v>46305</v>
       </c>
       <c r="E128" s="100"/>
-      <c r="F128" s="139"/>
-      <c r="G128" s="144"/>
+      <c r="F128" s="138"/>
+      <c r="G128" s="143"/>
       <c r="H128" s="101"/>
     </row>
-    <row r="129" spans="1:8" ht="24.75" customHeight="1">
+    <row r="129" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="80" t="s">
         <v>243</v>
       </c>
@@ -15018,11 +15024,11 @@
         <v>46305</v>
       </c>
       <c r="E129" s="100"/>
-      <c r="F129" s="139"/>
-      <c r="G129" s="144"/>
+      <c r="F129" s="138"/>
+      <c r="G129" s="143"/>
       <c r="H129" s="101"/>
     </row>
-    <row r="130" spans="1:8" ht="24.75" customHeight="1">
+    <row r="130" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="63" t="s">
         <v>243</v>
       </c>
@@ -15034,11 +15040,11 @@
         <v>46305</v>
       </c>
       <c r="E130" s="56"/>
-      <c r="F130" s="139"/>
-      <c r="G130" s="144"/>
+      <c r="F130" s="138"/>
+      <c r="G130" s="143"/>
       <c r="H130" s="101"/>
     </row>
-    <row r="131" spans="1:8" ht="24.75" customHeight="1">
+    <row r="131" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="111" t="s">
         <v>251</v>
       </c>
@@ -15050,11 +15056,11 @@
         <v>46305</v>
       </c>
       <c r="E131" s="56"/>
-      <c r="F131" s="139"/>
-      <c r="G131" s="144"/>
+      <c r="F131" s="138"/>
+      <c r="G131" s="143"/>
       <c r="H131" s="101"/>
     </row>
-    <row r="132" spans="1:8" ht="24.75" customHeight="1">
+    <row r="132" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="74" t="s">
         <v>251</v>
       </c>
@@ -15066,11 +15072,11 @@
         <v>46305</v>
       </c>
       <c r="E132" s="56"/>
-      <c r="F132" s="139"/>
-      <c r="G132" s="144"/>
+      <c r="F132" s="138"/>
+      <c r="G132" s="143"/>
       <c r="H132" s="101"/>
     </row>
-    <row r="133" spans="1:8" ht="24.75" customHeight="1">
+    <row r="133" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="77" t="s">
         <v>251</v>
       </c>
@@ -15082,11 +15088,11 @@
         <v>46305</v>
       </c>
       <c r="E133" s="100"/>
-      <c r="F133" s="139"/>
-      <c r="G133" s="144"/>
+      <c r="F133" s="138"/>
+      <c r="G133" s="143"/>
       <c r="H133" s="101"/>
     </row>
-    <row r="134" spans="1:8" ht="24.75" customHeight="1">
+    <row r="134" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="74" t="s">
         <v>251</v>
       </c>
@@ -15098,11 +15104,11 @@
         <v>46305</v>
       </c>
       <c r="E134" s="100"/>
-      <c r="F134" s="139"/>
-      <c r="G134" s="144"/>
+      <c r="F134" s="138"/>
+      <c r="G134" s="143"/>
       <c r="H134" s="101"/>
     </row>
-    <row r="135" spans="1:8" ht="24.75" customHeight="1">
+    <row r="135" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="77" t="s">
         <v>251</v>
       </c>
@@ -15114,11 +15120,11 @@
         <v>257</v>
       </c>
       <c r="E135" s="100"/>
-      <c r="F135" s="139"/>
-      <c r="G135" s="144"/>
+      <c r="F135" s="138"/>
+      <c r="G135" s="143"/>
       <c r="H135" s="101"/>
     </row>
-    <row r="136" spans="1:8" ht="24.75" customHeight="1">
+    <row r="136" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="74" t="s">
         <v>251</v>
       </c>
@@ -15130,11 +15136,11 @@
         <v>46305</v>
       </c>
       <c r="E136" s="100"/>
-      <c r="F136" s="139"/>
-      <c r="G136" s="144"/>
+      <c r="F136" s="138"/>
+      <c r="G136" s="143"/>
       <c r="H136" s="101"/>
     </row>
-    <row r="137" spans="1:8" ht="24.75" customHeight="1">
+    <row r="137" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="80" t="s">
         <v>251</v>
       </c>
@@ -15145,72 +15151,72 @@
       <c r="D137" s="113">
         <v>46305</v>
       </c>
-      <c r="E137" s="148"/>
-      <c r="F137" s="149"/>
-      <c r="G137" s="144"/>
-      <c r="H137" s="155"/>
-    </row>
-    <row r="138" spans="1:8" ht="24.75" customHeight="1">
+      <c r="E137" s="147"/>
+      <c r="F137" s="148"/>
+      <c r="G137" s="143"/>
+      <c r="H137" s="154"/>
+    </row>
+    <row r="138" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="130" t="s">
         <v>260</v>
       </c>
       <c r="B138" s="123"/>
       <c r="C138" s="123"/>
-      <c r="D138" s="147"/>
-      <c r="E138" s="144"/>
-      <c r="F138" s="134"/>
-      <c r="G138" s="144"/>
-      <c r="H138" s="134"/>
-    </row>
-    <row r="139" spans="1:8" ht="24.75" customHeight="1">
+      <c r="D138" s="146"/>
+      <c r="E138" s="143"/>
+      <c r="F138" s="133"/>
+      <c r="G138" s="143"/>
+      <c r="H138" s="133"/>
+    </row>
+    <row r="139" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="129" t="s">
         <v>260</v>
       </c>
       <c r="B139" s="61"/>
       <c r="C139" s="61"/>
       <c r="D139" s="113"/>
-      <c r="E139" s="144"/>
-      <c r="F139" s="134"/>
-      <c r="G139" s="144"/>
-      <c r="H139" s="134"/>
-    </row>
-    <row r="140" spans="1:8" ht="24.75" customHeight="1">
+      <c r="E139" s="143"/>
+      <c r="F139" s="133"/>
+      <c r="G139" s="143"/>
+      <c r="H139" s="133"/>
+    </row>
+    <row r="140" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="130" t="s">
         <v>261</v>
       </c>
       <c r="B140" s="123"/>
       <c r="C140" s="123"/>
-      <c r="D140" s="147"/>
-      <c r="E140" s="144"/>
-      <c r="F140" s="134"/>
-      <c r="G140" s="144"/>
-      <c r="H140" s="134"/>
-    </row>
-    <row r="141" spans="1:8" ht="24.75" customHeight="1">
+      <c r="D140" s="146"/>
+      <c r="E140" s="143"/>
+      <c r="F140" s="133"/>
+      <c r="G140" s="143"/>
+      <c r="H140" s="133"/>
+    </row>
+    <row r="141" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="129" t="s">
         <v>261</v>
       </c>
       <c r="B141" s="61"/>
       <c r="C141" s="61"/>
       <c r="D141" s="113"/>
-      <c r="E141" s="145"/>
-      <c r="F141" s="154"/>
-      <c r="G141" s="145"/>
-      <c r="H141" s="134"/>
-    </row>
-    <row r="142" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A142" s="158" t="s">
+      <c r="E141" s="144"/>
+      <c r="F141" s="153"/>
+      <c r="G141" s="144"/>
+      <c r="H141" s="133"/>
+    </row>
+    <row r="142" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A142" s="157" t="s">
         <v>262</v>
       </c>
-      <c r="B142" s="158"/>
-      <c r="C142" s="158"/>
-      <c r="D142" s="158"/>
-      <c r="E142" s="158"/>
-      <c r="F142" s="158"/>
-      <c r="G142" s="158"/>
-      <c r="H142" s="158"/>
-    </row>
-    <row r="143" spans="1:8" ht="24.75" customHeight="1">
+      <c r="B142" s="157"/>
+      <c r="C142" s="157"/>
+      <c r="D142" s="157"/>
+      <c r="E142" s="157"/>
+      <c r="F142" s="157"/>
+      <c r="G142" s="157"/>
+      <c r="H142" s="157"/>
+    </row>
+    <row r="143" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="77" t="s">
         <v>263</v>
       </c>
@@ -15222,11 +15228,11 @@
         <v>46305</v>
       </c>
       <c r="E143" s="52"/>
-      <c r="F143" s="138"/>
-      <c r="G143" s="146"/>
+      <c r="F143" s="137"/>
+      <c r="G143" s="145"/>
       <c r="H143" s="103"/>
     </row>
-    <row r="144" spans="1:8" ht="24.75" customHeight="1">
+    <row r="144" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="74" t="s">
         <v>263</v>
       </c>
@@ -15238,11 +15244,11 @@
         <v>46336</v>
       </c>
       <c r="E144" s="56"/>
-      <c r="F144" s="139"/>
-      <c r="G144" s="144"/>
+      <c r="F144" s="138"/>
+      <c r="G144" s="143"/>
       <c r="H144" s="101"/>
     </row>
-    <row r="145" spans="1:8" ht="24.75" customHeight="1">
+    <row r="145" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="77" t="s">
         <v>263</v>
       </c>
@@ -15254,11 +15260,11 @@
         <v>46305</v>
       </c>
       <c r="E145" s="56"/>
-      <c r="F145" s="139"/>
-      <c r="G145" s="144"/>
+      <c r="F145" s="138"/>
+      <c r="G145" s="143"/>
       <c r="H145" s="101"/>
     </row>
-    <row r="146" spans="1:8" ht="24.75" customHeight="1">
+    <row r="146" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="74" t="s">
         <v>263</v>
       </c>
@@ -15270,11 +15276,11 @@
         <v>46336</v>
       </c>
       <c r="E146" s="56"/>
-      <c r="F146" s="139"/>
-      <c r="G146" s="144"/>
+      <c r="F146" s="138"/>
+      <c r="G146" s="143"/>
       <c r="H146" s="101"/>
     </row>
-    <row r="147" spans="1:8" ht="24.75" customHeight="1">
+    <row r="147" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="77" t="s">
         <v>263</v>
       </c>
@@ -15286,11 +15292,11 @@
         <v>46305</v>
       </c>
       <c r="E147" s="56"/>
-      <c r="F147" s="139"/>
-      <c r="G147" s="144"/>
+      <c r="F147" s="138"/>
+      <c r="G147" s="143"/>
       <c r="H147" s="101"/>
     </row>
-    <row r="148" spans="1:8" ht="24.75" customHeight="1">
+    <row r="148" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="74" t="s">
         <v>263</v>
       </c>
@@ -15302,11 +15308,11 @@
         <v>46336</v>
       </c>
       <c r="E148" s="56"/>
-      <c r="F148" s="139"/>
-      <c r="G148" s="144"/>
+      <c r="F148" s="138"/>
+      <c r="G148" s="143"/>
       <c r="H148" s="101"/>
     </row>
-    <row r="149" spans="1:8" ht="24.75" customHeight="1">
+    <row r="149" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="98" t="s">
         <v>263</v>
       </c>
@@ -15318,8 +15324,8 @@
         <v>46305</v>
       </c>
       <c r="E149" s="56"/>
-      <c r="F149" s="139"/>
-      <c r="G149" s="144"/>
+      <c r="F149" s="138"/>
+      <c r="G149" s="143"/>
       <c r="H149" s="101"/>
     </row>
   </sheetData>
@@ -15331,12 +15337,12 @@
     <mergeCell ref="A142:H142"/>
     <mergeCell ref="A3:H3"/>
   </mergeCells>
-  <conditionalFormatting sqref="E1:E2 E4:E38 E40:E82 E84:E94 E96:E141 E143:E1048576">
+  <conditionalFormatting sqref="E1:E2 F2 E4:E38 E40:E82 E84:E94 E96:E141 E143:E1048576">
     <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="Si">
       <formula>NOT(ISERROR(SEARCH("Si",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F2 F4:F38 F40:F82 F84:F94 F96:F141 F143:F1048576">
+  <conditionalFormatting sqref="F1 F4:F38 F40:F82 F84:F94 F96:F141 F143:F1048576">
     <cfRule type="containsText" dxfId="2" priority="6" operator="containsText" text="Aprobado">
       <formula>NOT(ISERROR(SEARCH("Aprobado",F1)))</formula>
     </cfRule>
